--- a/IM/202608_Service_Count_Report.xlsx
+++ b/IM/202608_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$104</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$106</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="381">
   <si>
     <t>服務次數統計表        篩選月份：202608</t>
   </si>
@@ -459,6 +459,27 @@
   </si>
   <si>
     <t>定位點跑掉，重新定位</t>
+  </si>
+  <si>
+    <t>15:10:00</t>
+  </si>
+  <si>
+    <t>15:32:00</t>
+  </si>
+  <si>
+    <t>THILF0C672</t>
+  </si>
+  <si>
+    <t>新北市中和區中山路2段352號</t>
+  </si>
+  <si>
+    <t>中和橋安店</t>
+  </si>
+  <si>
+    <t>15:50:00</t>
+  </si>
+  <si>
+    <t>檢查排線 重新校正</t>
   </si>
   <si>
     <t>12:20:00</t>
@@ -1569,7 +1590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB104"/>
+  <dimension ref="A1:AB106"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -3037,7 +3058,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026080762</v>
+        <v>2026080761</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -3074,7 +3095,7 @@
       </c>
       <c r="N22" s="6"/>
       <c r="O22" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3">
@@ -3083,7 +3104,9 @@
       <c r="R22" s="3">
         <v>831722</v>
       </c>
-      <c r="S22" s="3"/>
+      <c r="S22" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
@@ -3103,7 +3126,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026080761</v>
+        <v>2026080762</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -3140,7 +3163,7 @@
       </c>
       <c r="N23" s="8"/>
       <c r="O23" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P23" s="7"/>
       <c r="Q23" s="7">
@@ -3149,9 +3172,7 @@
       <c r="R23" s="7">
         <v>831722</v>
       </c>
-      <c r="S23" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S23" s="7"/>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -3509,7 +3530,7 @@
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026080090</v>
+        <v>2026080999</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -3521,7 +3542,7 @@
         <v>30</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>143</v>
@@ -3577,7 +3598,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026080005</v>
+        <v>2026080946</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -3589,7 +3610,7 @@
         <v>30</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>144</v>
@@ -3643,7 +3664,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026080224</v>
+        <v>2026080090</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -3655,7 +3676,7 @@
         <v>30</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>150</v>
@@ -3666,20 +3687,16 @@
       <c r="I31" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="J31" s="7" t="s">
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="M31" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="K31" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L31" s="8" t="s">
+      <c r="N31" s="8" t="s">
         <v>154</v>
-      </c>
-      <c r="M31" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="N31" s="8" t="s">
-        <v>156</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>39</v>
@@ -3687,7 +3704,7 @@
       <c r="P31" s="7"/>
       <c r="Q31" s="7"/>
       <c r="R31" s="7">
-        <v>2688</v>
+        <v>0</v>
       </c>
       <c r="S31" s="7" t="s">
         <v>40</v>
@@ -3697,9 +3714,11 @@
       <c r="V31" s="7"/>
       <c r="W31" s="7"/>
       <c r="X31" s="7"/>
-      <c r="Y31" s="7"/>
+      <c r="Y31" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z31" s="8" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="AA31" s="7" t="s">
         <v>40</v>
@@ -3713,7 +3732,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026080936</v>
+        <v>2026080005</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3722,50 +3741,44 @@
         <v>29</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>157</v>
+        <v>30</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P32" s="3">
-        <v>8160</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>17940</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
       <c r="R32" s="3">
-        <v>26200</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -3773,21 +3786,19 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB32" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB32" s="3"/>
     </row>
     <row r="33" spans="1:28">
       <c r="A33" s="7">
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026080937</v>
+        <v>2026080224</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3796,48 +3807,46 @@
         <v>29</v>
       </c>
       <c r="E33" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G33" s="7" t="s">
+      <c r="H33" s="7" t="s">
         <v>158</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="I33" s="7" t="s">
         <v>159</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>53</v>
+        <v>160</v>
       </c>
       <c r="K33" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>37</v>
+        <v>161</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="P33" s="7">
-        <v>8160</v>
-      </c>
-      <c r="Q33" s="7">
-        <v>17940</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
       <c r="R33" s="7">
-        <v>26200</v>
-      </c>
-      <c r="S33" s="7"/>
+        <v>2688</v>
+      </c>
+      <c r="S33" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
       <c r="V33" s="7"/>
@@ -3845,19 +3854,21 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8" t="s">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="AA33" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB33" s="7"/>
+      <c r="AB33" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:28">
       <c r="A34" s="3">
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026080115</v>
+        <v>2026080936</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3866,19 +3877,19 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>53</v>
@@ -3887,23 +3898,25 @@
         <v>36</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>165</v>
+        <v>37</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P34" s="3"/>
+      <c r="P34" s="3">
+        <v>8160</v>
+      </c>
       <c r="Q34" s="3">
-        <v>2754</v>
+        <v>17940</v>
       </c>
       <c r="R34" s="3">
-        <v>153369</v>
+        <v>26200</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>40</v>
@@ -3915,17 +3928,21 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA34" s="3"/>
-      <c r="AB34" s="3"/>
+        <v>169</v>
+      </c>
+      <c r="AA34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="35" spans="1:28">
       <c r="A35" s="7">
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026080116</v>
+        <v>2026080937</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3934,19 +3951,19 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>53</v>
@@ -3955,23 +3972,25 @@
         <v>36</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>165</v>
+        <v>37</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O35" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="P35" s="7"/>
+      <c r="P35" s="7">
+        <v>8160</v>
+      </c>
       <c r="Q35" s="7">
-        <v>2754</v>
+        <v>17940</v>
       </c>
       <c r="R35" s="7">
-        <v>153369</v>
+        <v>26200</v>
       </c>
       <c r="S35" s="7"/>
       <c r="T35" s="7"/>
@@ -3981,9 +4000,11 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA35" s="7"/>
+        <v>169</v>
+      </c>
+      <c r="AA35" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB35" s="7"/>
     </row>
     <row r="36" spans="1:28">
@@ -3991,7 +4012,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026080128</v>
+        <v>2026080115</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -4000,19 +4021,19 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>169</v>
+        <v>43</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>53</v>
@@ -4021,21 +4042,23 @@
         <v>36</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="N36" s="6"/>
+        <v>173</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>174</v>
+      </c>
       <c r="O36" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P36" s="3"/>
       <c r="Q36" s="3">
-        <v>636</v>
+        <v>2754</v>
       </c>
       <c r="R36" s="3">
-        <v>26641</v>
+        <v>153369</v>
       </c>
       <c r="S36" s="3" t="s">
         <v>40</v>
@@ -4047,21 +4070,17 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA36" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB36" s="3">
-        <v>1</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3"/>
     </row>
     <row r="37" spans="1:28">
       <c r="A37" s="7">
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026080129</v>
+        <v>2026080116</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -4070,19 +4089,19 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>169</v>
+        <v>43</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J37" s="7" t="s">
         <v>53</v>
@@ -4091,21 +4110,23 @@
         <v>36</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="N37" s="8"/>
+        <v>173</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>174</v>
+      </c>
       <c r="O37" s="7" t="s">
         <v>64</v>
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7">
-        <v>636</v>
+        <v>2754</v>
       </c>
       <c r="R37" s="7">
-        <v>26641</v>
+        <v>153369</v>
       </c>
       <c r="S37" s="7"/>
       <c r="T37" s="7"/>
@@ -4115,11 +4136,9 @@
       <c r="X37" s="7"/>
       <c r="Y37" s="7"/>
       <c r="Z37" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA37" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="AA37" s="7"/>
       <c r="AB37" s="7"/>
     </row>
     <row r="38" spans="1:28">
@@ -4127,7 +4146,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026080653</v>
+        <v>2026080128</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -4136,42 +4155,42 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="N38" s="6" t="s">
-        <v>178</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N38" s="6"/>
       <c r="O38" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
+      <c r="Q38" s="3">
+        <v>636</v>
+      </c>
       <c r="R38" s="3">
-        <v>30354</v>
+        <v>26641</v>
       </c>
       <c r="S38" s="3" t="s">
         <v>40</v>
@@ -4183,7 +4202,7 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AA38" s="3" t="s">
         <v>40</v>
@@ -4197,7 +4216,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026080654</v>
+        <v>2026080129</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -4206,42 +4225,42 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="N39" s="8" t="s">
-        <v>178</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="N39" s="8"/>
       <c r="O39" s="7" t="s">
         <v>64</v>
       </c>
       <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
+      <c r="Q39" s="7">
+        <v>636</v>
+      </c>
       <c r="R39" s="7">
-        <v>30354</v>
+        <v>26641</v>
       </c>
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
@@ -4251,7 +4270,7 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AA39" s="7" t="s">
         <v>40</v>
@@ -4263,7 +4282,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026080571</v>
+        <v>2026080653</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -4272,19 +4291,19 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>99</v>
+        <v>180</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>77</v>
@@ -4293,31 +4312,33 @@
         <v>36</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="N40" s="6"/>
+        <v>184</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>185</v>
+      </c>
       <c r="O40" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3">
-        <v>53103</v>
-      </c>
-      <c r="S40" s="3"/>
+        <v>30354</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T40" s="3"/>
-      <c r="U40" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="AA40" s="3" t="s">
         <v>40</v>
@@ -4331,7 +4352,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>2026080623</v>
+        <v>2026080654</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -4340,40 +4361,42 @@
         <v>29</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>123</v>
+        <v>180</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="N41" s="8"/>
+        <v>184</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>185</v>
+      </c>
       <c r="O41" s="7" t="s">
         <v>64</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="7">
-        <v>38400</v>
+        <v>30354</v>
       </c>
       <c r="S41" s="7"/>
       <c r="T41" s="7"/>
@@ -4383,21 +4406,19 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="8" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AA41" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB41" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB41" s="7"/>
     </row>
     <row r="42" spans="1:28">
       <c r="A42" s="3">
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2026080077</v>
+        <v>2026080571</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -4406,42 +4427,40 @@
         <v>29</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>192</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N42" s="6"/>
       <c r="O42" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3">
-        <v>125866</v>
+        <v>53103</v>
       </c>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
@@ -4453,17 +4472,21 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA42" s="3"/>
-      <c r="AB42" s="3"/>
+        <v>190</v>
+      </c>
+      <c r="AA42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:28">
       <c r="A43" s="7">
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026080075</v>
+        <v>2026080623</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -4472,19 +4495,19 @@
         <v>29</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>193</v>
+        <v>123</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>83</v>
@@ -4493,25 +4516,21 @@
         <v>36</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="M43" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="N43" s="8" t="s">
-        <v>192</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N43" s="8"/>
       <c r="O43" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7">
-        <v>135251</v>
-      </c>
-      <c r="S43" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>38400</v>
+      </c>
+      <c r="S43" s="7"/>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
@@ -4519,17 +4538,21 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA43" s="7"/>
-      <c r="AB43" s="7"/>
+        <v>169</v>
+      </c>
+      <c r="AA43" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB43" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:28">
       <c r="A44" s="3">
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026080076</v>
+        <v>2026080077</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -4538,19 +4561,19 @@
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>194</v>
+        <v>50</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>83</v>
@@ -4559,31 +4582,33 @@
         <v>36</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3">
-        <v>135251</v>
+        <v>125866</v>
       </c>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
-      <c r="U44" s="3"/>
+      <c r="U44" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="6" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
@@ -4593,7 +4618,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>2026080073</v>
+        <v>2026080075</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -4602,19 +4627,19 @@
         <v>29</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J45" s="7" t="s">
         <v>83</v>
@@ -4623,13 +4648,13 @@
         <v>36</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="O45" s="7" t="s">
         <v>39</v>
@@ -4637,7 +4662,7 @@
       <c r="P45" s="7"/>
       <c r="Q45" s="7"/>
       <c r="R45" s="7">
-        <v>6329</v>
+        <v>135251</v>
       </c>
       <c r="S45" s="7" t="s">
         <v>40</v>
@@ -4649,7 +4674,7 @@
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="8" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AA45" s="7"/>
       <c r="AB45" s="7"/>
@@ -4659,7 +4684,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2026080074</v>
+        <v>2026080076</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -4668,19 +4693,19 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>83</v>
@@ -4689,13 +4714,13 @@
         <v>36</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>64</v>
@@ -4703,7 +4728,7 @@
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3">
-        <v>6329</v>
+        <v>135251</v>
       </c>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
@@ -4713,7 +4738,7 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
@@ -4723,7 +4748,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026080629</v>
+        <v>2026080073</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4732,44 +4757,42 @@
         <v>29</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>199</v>
+        <v>83</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="O47" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P47" s="7"/>
-      <c r="Q47" s="7">
-        <v>3160</v>
-      </c>
+      <c r="Q47" s="7"/>
       <c r="R47" s="7">
-        <v>415812</v>
+        <v>6329</v>
       </c>
       <c r="S47" s="7" t="s">
         <v>40</v>
@@ -4781,21 +4804,17 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA47" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB47" s="7">
-        <v>1</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="AA47" s="7"/>
+      <c r="AB47" s="7"/>
     </row>
     <row r="48" spans="1:28">
       <c r="A48" s="3">
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026080630</v>
+        <v>2026080074</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -4804,44 +4823,42 @@
         <v>29</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>196</v>
+        <v>50</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>199</v>
+        <v>83</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>64</v>
       </c>
       <c r="P48" s="3"/>
-      <c r="Q48" s="3">
-        <v>3160</v>
-      </c>
+      <c r="Q48" s="3"/>
       <c r="R48" s="3">
-        <v>415812</v>
+        <v>6329</v>
       </c>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
@@ -4851,11 +4868,9 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="AA48" s="3"/>
       <c r="AB48" s="3"/>
     </row>
     <row r="49" spans="1:28">
@@ -4863,7 +4878,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>2026080408</v>
+        <v>2026080629</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -4872,54 +4887,56 @@
         <v>29</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>32</v>
+        <v>203</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="O49" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
+      <c r="Q49" s="7">
+        <v>3160</v>
+      </c>
       <c r="R49" s="7">
-        <v>0</v>
-      </c>
-      <c r="S49" s="7"/>
-      <c r="T49" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>415812</v>
+      </c>
+      <c r="S49" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T49" s="7"/>
       <c r="U49" s="7"/>
       <c r="V49" s="7"/>
       <c r="W49" s="7"/>
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
       <c r="Z49" s="8" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="AA49" s="7" t="s">
         <v>40</v>
@@ -4933,7 +4950,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2026080440</v>
+        <v>2026080630</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4942,48 +4959,46 @@
         <v>29</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>116</v>
+        <v>203</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>108</v>
+        <v>206</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P50" s="3"/>
       <c r="Q50" s="3">
-        <v>7167</v>
+        <v>3160</v>
       </c>
       <c r="R50" s="3">
-        <v>39533</v>
-      </c>
-      <c r="S50" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>415812</v>
+      </c>
+      <c r="S50" s="3"/>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
@@ -4991,9 +5006,11 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA50" s="3"/>
+        <v>169</v>
+      </c>
+      <c r="AA50" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="AB50" s="3"/>
     </row>
     <row r="51" spans="1:28">
@@ -5001,7 +5018,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="7">
-        <v>2026080441</v>
+        <v>2026080408</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -5010,64 +5027,68 @@
         <v>29</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>108</v>
+        <v>206</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P51" s="7"/>
-      <c r="Q51" s="7">
-        <v>7167</v>
-      </c>
+      <c r="Q51" s="7"/>
       <c r="R51" s="7">
-        <v>39533</v>
+        <v>0</v>
       </c>
       <c r="S51" s="7"/>
-      <c r="T51" s="7"/>
+      <c r="T51" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
       <c r="W51" s="7"/>
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="AA51" s="7"/>
-      <c r="AB51" s="7"/>
+        <v>214</v>
+      </c>
+      <c r="AA51" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB51" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:28">
       <c r="A52" s="3">
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>2026080112</v>
+        <v>2026080440</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -5076,56 +5097,56 @@
         <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>215</v>
+        <v>108</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
+      <c r="Q52" s="3">
+        <v>7167</v>
+      </c>
       <c r="R52" s="3">
-        <v>251357</v>
+        <v>39533</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>40</v>
       </c>
       <c r="T52" s="3"/>
-      <c r="U52" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="6" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="AA52" s="3"/>
       <c r="AB52" s="3"/>
@@ -5135,7 +5156,7 @@
         <v>51</v>
       </c>
       <c r="B53" s="7">
-        <v>2026080113</v>
+        <v>2026080441</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -5144,42 +5165,44 @@
         <v>29</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>215</v>
+        <v>108</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N53" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O53" s="7" t="s">
         <v>64</v>
       </c>
       <c r="P53" s="7"/>
-      <c r="Q53" s="7"/>
+      <c r="Q53" s="7">
+        <v>7167</v>
+      </c>
       <c r="R53" s="7">
-        <v>251357</v>
+        <v>39533</v>
       </c>
       <c r="S53" s="7"/>
       <c r="T53" s="7"/>
@@ -5189,7 +5212,7 @@
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
       <c r="Z53" s="8" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="AA53" s="7"/>
       <c r="AB53" s="7"/>
@@ -5199,7 +5222,7 @@
         <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>2026080938</v>
+        <v>2026080112</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -5208,56 +5231,56 @@
         <v>29</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>98</v>
+        <v>220</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>113</v>
+        <v>222</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P54" s="3"/>
-      <c r="Q54" s="3">
-        <v>3815</v>
-      </c>
+      <c r="Q54" s="3"/>
       <c r="R54" s="3">
-        <v>225709</v>
+        <v>251357</v>
       </c>
       <c r="S54" s="3" t="s">
         <v>40</v>
       </c>
       <c r="T54" s="3"/>
-      <c r="U54" s="3"/>
+      <c r="U54" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="6" t="s">
-        <v>162</v>
+        <v>225</v>
       </c>
       <c r="AA54" s="3"/>
       <c r="AB54" s="3"/>
@@ -5267,7 +5290,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="7">
-        <v>2026080939</v>
+        <v>2026080113</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -5276,44 +5299,42 @@
         <v>29</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>98</v>
+        <v>220</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>113</v>
+        <v>222</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O55" s="7" t="s">
         <v>64</v>
       </c>
       <c r="P55" s="7"/>
-      <c r="Q55" s="7">
-        <v>3815</v>
-      </c>
+      <c r="Q55" s="7"/>
       <c r="R55" s="7">
-        <v>225709</v>
+        <v>251357</v>
       </c>
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
@@ -5323,7 +5344,7 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="8" t="s">
-        <v>162</v>
+        <v>225</v>
       </c>
       <c r="AA55" s="7"/>
       <c r="AB55" s="7"/>
@@ -5333,7 +5354,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>2026080940</v>
+        <v>2026080939</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
@@ -5342,19 +5363,19 @@
         <v>29</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>95</v>
+        <v>226</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>224</v>
+        <v>98</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>113</v>
@@ -5363,27 +5384,25 @@
         <v>36</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="O56" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P56" s="3"/>
       <c r="Q56" s="3">
-        <v>11287</v>
+        <v>3815</v>
       </c>
       <c r="R56" s="3">
-        <v>310496</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>225709</v>
+      </c>
+      <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
@@ -5391,7 +5410,7 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
@@ -5401,7 +5420,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="7">
-        <v>2026080941</v>
+        <v>2026080938</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -5410,19 +5429,19 @@
         <v>29</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>95</v>
+        <v>226</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>224</v>
+        <v>98</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J57" s="7" t="s">
         <v>113</v>
@@ -5431,25 +5450,27 @@
         <v>36</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="N57" s="8" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="O57" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P57" s="7"/>
       <c r="Q57" s="7">
-        <v>11287</v>
+        <v>3815</v>
       </c>
       <c r="R57" s="7">
-        <v>310496</v>
-      </c>
-      <c r="S57" s="7"/>
+        <v>225709</v>
+      </c>
+      <c r="S57" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T57" s="7"/>
       <c r="U57" s="7"/>
       <c r="V57" s="7"/>
@@ -5457,7 +5478,7 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="8" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="AA57" s="7"/>
       <c r="AB57" s="7"/>
@@ -5467,7 +5488,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>2026080681</v>
+        <v>2026080940</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -5476,38 +5497,44 @@
         <v>29</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I58" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L58" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>229</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P58" s="3"/>
-      <c r="Q58" s="3"/>
+      <c r="Q58" s="3">
+        <v>11287</v>
+      </c>
       <c r="R58" s="3">
-        <v>0</v>
+        <v>310496</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>40</v>
@@ -5519,21 +5546,17 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>1</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="AA58" s="3"/>
+      <c r="AB58" s="3"/>
     </row>
     <row r="59" spans="1:28">
       <c r="A59" s="7">
         <v>57</v>
       </c>
       <c r="B59" s="7">
-        <v>2026080993</v>
+        <v>2026080941</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -5542,64 +5565,64 @@
         <v>29</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G59" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H59" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="H59" s="7" t="s">
+      <c r="I59" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="I59" s="7" t="s">
+      <c r="J59" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="N59" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="J59" s="7"/>
-      <c r="K59" s="7"/>
-      <c r="L59" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="M59" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="N59" s="8" t="s">
-        <v>235</v>
-      </c>
       <c r="O59" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P59" s="7"/>
-      <c r="Q59" s="7"/>
+      <c r="Q59" s="7">
+        <v>11287</v>
+      </c>
       <c r="R59" s="7">
-        <v>0</v>
+        <v>310496</v>
       </c>
       <c r="S59" s="7"/>
-      <c r="T59" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="T59" s="7"/>
       <c r="U59" s="7"/>
       <c r="V59" s="7"/>
       <c r="W59" s="7"/>
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
       <c r="Z59" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA59" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB59" s="7">
-        <v>1</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="AA59" s="7"/>
+      <c r="AB59" s="7"/>
     </row>
     <row r="60" spans="1:28">
       <c r="A60" s="3">
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>2026080656</v>
+        <v>2026080681</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -5608,19 +5631,19 @@
         <v>29</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>136</v>
+        <v>43</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
@@ -5628,10 +5651,10 @@
         <v>119</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>39</v>
@@ -5665,7 +5688,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="7">
-        <v>2026080705</v>
+        <v>2026080993</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5674,19 +5697,19 @@
         <v>29</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>116</v>
+        <v>238</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
@@ -5694,10 +5717,10 @@
         <v>119</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N61" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="O61" s="7" t="s">
         <v>39</v>
@@ -5707,17 +5730,17 @@
       <c r="R61" s="7">
         <v>0</v>
       </c>
-      <c r="S61" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T61" s="7"/>
+      <c r="S61" s="7"/>
+      <c r="T61" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="U61" s="7"/>
       <c r="V61" s="7"/>
       <c r="W61" s="7"/>
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="8" t="s">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="AA61" s="7" t="s">
         <v>40</v>
@@ -5731,7 +5754,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="3">
-        <v>2026080746</v>
+        <v>2026080656</v>
       </c>
       <c r="C62" s="3">
         <v>1</v>
@@ -5740,19 +5763,19 @@
         <v>29</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="H62" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
@@ -5760,10 +5783,10 @@
         <v>119</v>
       </c>
       <c r="M62" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="N62" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="N62" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>39</v>
@@ -5783,7 +5806,7 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
       <c r="Z62" s="6" t="s">
-        <v>249</v>
+        <v>122</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>40</v>
@@ -5797,7 +5820,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="7">
-        <v>2026080561</v>
+        <v>2026080705</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
@@ -5806,48 +5829,42 @@
         <v>29</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>32</v>
+        <v>248</v>
       </c>
       <c r="I63" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+      <c r="L63" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="N63" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="J63" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="K63" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L63" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="M63" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="N63" s="8" t="s">
-        <v>253</v>
-      </c>
       <c r="O63" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="P63" s="7">
-        <v>2745</v>
-      </c>
-      <c r="Q63" s="7">
-        <v>3684</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="P63" s="7"/>
+      <c r="Q63" s="7"/>
       <c r="R63" s="7">
-        <v>17102</v>
-      </c>
-      <c r="S63" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S63" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T63" s="7"/>
       <c r="U63" s="7"/>
       <c r="V63" s="7"/>
@@ -5855,7 +5872,7 @@
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
       <c r="Z63" s="8" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="AA63" s="7" t="s">
         <v>40</v>
@@ -5869,7 +5886,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="3">
-        <v>2026080560</v>
+        <v>2026080746</v>
       </c>
       <c r="C64" s="3">
         <v>1</v>
@@ -5878,48 +5895,42 @@
         <v>29</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G64" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M64" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="H64" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I64" s="3" t="s">
+      <c r="N64" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="J64" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M64" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="N64" s="6" t="s">
-        <v>257</v>
-      </c>
       <c r="O64" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="P64" s="3">
-        <v>937</v>
-      </c>
-      <c r="Q64" s="3">
-        <v>1866</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
       <c r="R64" s="3">
-        <v>12148</v>
-      </c>
-      <c r="S64" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
@@ -5927,7 +5938,7 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="6" t="s">
-        <v>41</v>
+        <v>256</v>
       </c>
       <c r="AA64" s="3" t="s">
         <v>40</v>
@@ -5941,7 +5952,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="7">
-        <v>2026080159</v>
+        <v>2026080561</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -5950,16 +5961,16 @@
         <v>29</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="I65" s="7" t="s">
         <v>258</v>
@@ -5971,7 +5982,7 @@
         <v>36</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="M65" s="8" t="s">
         <v>259</v>
@@ -5982,12 +5993,14 @@
       <c r="O65" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="P65" s="7"/>
+      <c r="P65" s="7">
+        <v>2745</v>
+      </c>
       <c r="Q65" s="7">
-        <v>730</v>
+        <v>3684</v>
       </c>
       <c r="R65" s="7">
-        <v>5615</v>
+        <v>17102</v>
       </c>
       <c r="S65" s="7"/>
       <c r="T65" s="7"/>
@@ -6011,7 +6024,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="3">
-        <v>2026080673</v>
+        <v>2026080560</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
@@ -6020,7 +6033,7 @@
         <v>29</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>42</v>
@@ -6029,10 +6042,10 @@
         <v>261</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>53</v>
@@ -6041,35 +6054,35 @@
         <v>36</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P66" s="3"/>
+        <v>64</v>
+      </c>
+      <c r="P66" s="3">
+        <v>937</v>
+      </c>
       <c r="Q66" s="3">
-        <v>730</v>
+        <v>1866</v>
       </c>
       <c r="R66" s="3">
-        <v>5615</v>
+        <v>12148</v>
       </c>
       <c r="S66" s="3"/>
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
-      <c r="W66" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="6" t="s">
-        <v>262</v>
+        <v>41</v>
       </c>
       <c r="AA66" s="3" t="s">
         <v>40</v>
@@ -6083,7 +6096,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="7">
-        <v>2026080908</v>
+        <v>2026080159</v>
       </c>
       <c r="C67" s="7">
         <v>1</v>
@@ -6092,42 +6105,44 @@
         <v>29</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>263</v>
+        <v>58</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>264</v>
+        <v>74</v>
       </c>
       <c r="I67" s="7" t="s">
         <v>265</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="K67" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L67" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="M67" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="M67" s="8" t="s">
+      <c r="N67" s="8" t="s">
         <v>267</v>
-      </c>
-      <c r="N67" s="8" t="s">
-        <v>268</v>
       </c>
       <c r="O67" s="7" t="s">
         <v>64</v>
       </c>
       <c r="P67" s="7"/>
-      <c r="Q67" s="7"/>
+      <c r="Q67" s="7">
+        <v>730</v>
+      </c>
       <c r="R67" s="7">
-        <v>3638</v>
+        <v>5615</v>
       </c>
       <c r="S67" s="7"/>
       <c r="T67" s="7"/>
@@ -6151,7 +6166,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="3">
-        <v>2026080679</v>
+        <v>2026080673</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -6160,52 +6175,56 @@
         <v>29</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>163</v>
+        <v>268</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>176</v>
+        <v>61</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O68" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P68" s="3"/>
-      <c r="Q68" s="3"/>
+      <c r="Q68" s="3">
+        <v>730</v>
+      </c>
       <c r="R68" s="3">
-        <v>59219</v>
+        <v>5615</v>
       </c>
       <c r="S68" s="3"/>
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
-      <c r="W68" s="3"/>
+      <c r="W68" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
       <c r="Z68" s="6" t="s">
-        <v>41</v>
+        <v>269</v>
       </c>
       <c r="AA68" s="3" t="s">
         <v>40</v>
@@ -6219,7 +6238,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="7">
-        <v>2026080680</v>
+        <v>2026080908</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -6228,16 +6247,16 @@
         <v>29</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>43</v>
+        <v>270</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="I69" s="7" t="s">
         <v>272</v>
@@ -6249,13 +6268,13 @@
         <v>36</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>176</v>
+        <v>273</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N69" s="8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O69" s="7" t="s">
         <v>64</v>
@@ -6263,7 +6282,7 @@
       <c r="P69" s="7"/>
       <c r="Q69" s="7"/>
       <c r="R69" s="7">
-        <v>94136</v>
+        <v>3638</v>
       </c>
       <c r="S69" s="7"/>
       <c r="T69" s="7"/>
@@ -6287,7 +6306,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="3">
-        <v>2026080562</v>
+        <v>2026080679</v>
       </c>
       <c r="C70" s="3">
         <v>1</v>
@@ -6296,28 +6315,28 @@
         <v>29</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>276</v>
+        <v>183</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>277</v>
@@ -6331,7 +6350,7 @@
       <c r="P70" s="3"/>
       <c r="Q70" s="3"/>
       <c r="R70" s="3">
-        <v>203813</v>
+        <v>59219</v>
       </c>
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
@@ -6355,7 +6374,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7">
-        <v>2026080563</v>
+        <v>2026080680</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -6364,28 +6383,28 @@
         <v>29</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="I71" s="7" t="s">
         <v>279</v>
       </c>
       <c r="J71" s="7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K71" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>276</v>
+        <v>183</v>
       </c>
       <c r="M71" s="8" t="s">
         <v>280</v>
@@ -6399,7 +6418,7 @@
       <c r="P71" s="7"/>
       <c r="Q71" s="7"/>
       <c r="R71" s="7">
-        <v>219373</v>
+        <v>94136</v>
       </c>
       <c r="S71" s="7"/>
       <c r="T71" s="7"/>
@@ -6423,7 +6442,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="3">
-        <v>2026080459</v>
+        <v>2026080562</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
@@ -6432,16 +6451,16 @@
         <v>29</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>241</v>
+        <v>32</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>74</v>
+        <v>226</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>282</v>
@@ -6453,21 +6472,21 @@
         <v>36</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>204</v>
+        <v>283</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P72" s="3"/>
       <c r="Q72" s="3"/>
       <c r="R72" s="3">
-        <v>60429</v>
+        <v>203813</v>
       </c>
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
@@ -6477,7 +6496,7 @@
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
       <c r="Z72" s="6" t="s">
-        <v>285</v>
+        <v>41</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>40</v>
@@ -6491,7 +6510,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7">
-        <v>2026080911</v>
+        <v>2026080563</v>
       </c>
       <c r="C73" s="7">
         <v>1</v>
@@ -6500,19 +6519,19 @@
         <v>29</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="H73" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I73" s="7" t="s">
         <v>286</v>
-      </c>
-      <c r="I73" s="7" t="s">
-        <v>287</v>
       </c>
       <c r="J73" s="7" t="s">
         <v>83</v>
@@ -6521,13 +6540,13 @@
         <v>36</v>
       </c>
       <c r="L73" s="8" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="M73" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="N73" s="8" t="s">
         <v>288</v>
-      </c>
-      <c r="N73" s="8" t="s">
-        <v>289</v>
       </c>
       <c r="O73" s="7" t="s">
         <v>64</v>
@@ -6535,7 +6554,7 @@
       <c r="P73" s="7"/>
       <c r="Q73" s="7"/>
       <c r="R73" s="7">
-        <v>9386</v>
+        <v>219373</v>
       </c>
       <c r="S73" s="7"/>
       <c r="T73" s="7"/>
@@ -6559,7 +6578,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="3">
-        <v>2026080747</v>
+        <v>2026080459</v>
       </c>
       <c r="C74" s="3">
         <v>1</v>
@@ -6568,19 +6587,19 @@
         <v>29</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G74" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="I74" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>83</v>
@@ -6589,21 +6608,21 @@
         <v>36</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="O74" s="3" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3">
-        <v>9338</v>
+        <v>60429</v>
       </c>
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
@@ -6613,7 +6632,7 @@
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
       <c r="Z74" s="6" t="s">
-        <v>41</v>
+        <v>292</v>
       </c>
       <c r="AA74" s="3" t="s">
         <v>40</v>
@@ -6627,7 +6646,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="7">
-        <v>2026080914</v>
+        <v>2026080911</v>
       </c>
       <c r="C75" s="7">
         <v>1</v>
@@ -6636,19 +6655,19 @@
         <v>29</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J75" s="7" t="s">
         <v>83</v>
@@ -6657,13 +6676,13 @@
         <v>36</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N75" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O75" s="7" t="s">
         <v>64</v>
@@ -6671,7 +6690,7 @@
       <c r="P75" s="7"/>
       <c r="Q75" s="7"/>
       <c r="R75" s="7">
-        <v>45877</v>
+        <v>9386</v>
       </c>
       <c r="S75" s="7"/>
       <c r="T75" s="7"/>
@@ -6695,7 +6714,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="3">
-        <v>2026080916</v>
+        <v>2026080747</v>
       </c>
       <c r="C76" s="3">
         <v>1</v>
@@ -6704,19 +6723,19 @@
         <v>29</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>83</v>
@@ -6725,13 +6744,13 @@
         <v>36</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>266</v>
+        <v>183</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>64</v>
@@ -6739,7 +6758,7 @@
       <c r="P76" s="3"/>
       <c r="Q76" s="3"/>
       <c r="R76" s="3">
-        <v>57194</v>
+        <v>9338</v>
       </c>
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
@@ -6763,7 +6782,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="7">
-        <v>2026080913</v>
+        <v>2026080914</v>
       </c>
       <c r="C77" s="7">
         <v>1</v>
@@ -6772,19 +6791,19 @@
         <v>29</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>66</v>
+        <v>226</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>219</v>
+        <v>106</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J77" s="7" t="s">
         <v>83</v>
@@ -6793,13 +6812,13 @@
         <v>36</v>
       </c>
       <c r="L77" s="8" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N77" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O77" s="7" t="s">
         <v>64</v>
@@ -6807,7 +6826,7 @@
       <c r="P77" s="7"/>
       <c r="Q77" s="7"/>
       <c r="R77" s="7">
-        <v>36587</v>
+        <v>45877</v>
       </c>
       <c r="S77" s="7"/>
       <c r="T77" s="7"/>
@@ -6831,7 +6850,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="3">
-        <v>2026080910</v>
+        <v>2026080916</v>
       </c>
       <c r="C78" s="3">
         <v>1</v>
@@ -6840,16 +6859,16 @@
         <v>29</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>302</v>
+        <v>95</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>158</v>
+        <v>268</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>303</v>
@@ -6861,7 +6880,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>304</v>
@@ -6875,7 +6894,7 @@
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
       <c r="R78" s="3">
-        <v>41847</v>
+        <v>57194</v>
       </c>
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
@@ -6899,7 +6918,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="7">
-        <v>2026080909</v>
+        <v>2026080913</v>
       </c>
       <c r="C79" s="7">
         <v>1</v>
@@ -6908,16 +6927,16 @@
         <v>29</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>264</v>
+        <v>66</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>306</v>
@@ -6929,7 +6948,7 @@
         <v>36</v>
       </c>
       <c r="L79" s="8" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="M79" s="8" t="s">
         <v>307</v>
@@ -6943,7 +6962,7 @@
       <c r="P79" s="7"/>
       <c r="Q79" s="7"/>
       <c r="R79" s="7">
-        <v>22007</v>
+        <v>36587</v>
       </c>
       <c r="S79" s="7"/>
       <c r="T79" s="7"/>
@@ -6967,7 +6986,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="3">
-        <v>2026080425</v>
+        <v>2026080910</v>
       </c>
       <c r="C80" s="3">
         <v>1</v>
@@ -6976,28 +6995,28 @@
         <v>29</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>136</v>
+        <v>309</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>310</v>
+        <v>83</v>
       </c>
       <c r="K80" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>204</v>
+        <v>273</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>311</v>
@@ -7009,11 +7028,9 @@
         <v>64</v>
       </c>
       <c r="P80" s="3"/>
-      <c r="Q80" s="3">
-        <v>2</v>
-      </c>
+      <c r="Q80" s="3"/>
       <c r="R80" s="3">
-        <v>6</v>
+        <v>41847</v>
       </c>
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
@@ -7037,7 +7054,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="7">
-        <v>2026080092</v>
+        <v>2026080909</v>
       </c>
       <c r="C81" s="7">
         <v>1</v>
@@ -7046,34 +7063,34 @@
         <v>29</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>163</v>
+        <v>309</v>
       </c>
       <c r="I81" s="7" t="s">
         <v>313</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="K81" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L81" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="M81" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="N81" s="8" t="s">
         <v>315</v>
-      </c>
-      <c r="M81" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="N81" s="8" t="s">
-        <v>317</v>
       </c>
       <c r="O81" s="7" t="s">
         <v>64</v>
@@ -7081,7 +7098,7 @@
       <c r="P81" s="7"/>
       <c r="Q81" s="7"/>
       <c r="R81" s="7">
-        <v>123517</v>
+        <v>22007</v>
       </c>
       <c r="S81" s="7"/>
       <c r="T81" s="7"/>
@@ -7105,7 +7122,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="3">
-        <v>2026080912</v>
+        <v>2026080425</v>
       </c>
       <c r="C82" s="3">
         <v>1</v>
@@ -7114,42 +7131,44 @@
         <v>29</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>286</v>
+        <v>136</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>266</v>
+        <v>211</v>
       </c>
       <c r="M82" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="N82" s="6" t="s">
         <v>319</v>
-      </c>
-      <c r="N82" s="6" t="s">
-        <v>320</v>
       </c>
       <c r="O82" s="3" t="s">
         <v>64</v>
       </c>
       <c r="P82" s="3"/>
-      <c r="Q82" s="3"/>
+      <c r="Q82" s="3">
+        <v>2</v>
+      </c>
       <c r="R82" s="3">
-        <v>1042</v>
+        <v>6</v>
       </c>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
@@ -7173,7 +7192,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="7">
-        <v>2026080915</v>
+        <v>2026080092</v>
       </c>
       <c r="C83" s="7">
         <v>1</v>
@@ -7182,34 +7201,34 @@
         <v>29</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="I83" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="J83" s="7" t="s">
         <v>321</v>
-      </c>
-      <c r="J83" s="7" t="s">
-        <v>314</v>
       </c>
       <c r="K83" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>266</v>
+        <v>322</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N83" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O83" s="7" t="s">
         <v>64</v>
@@ -7217,7 +7236,7 @@
       <c r="P83" s="7"/>
       <c r="Q83" s="7"/>
       <c r="R83" s="7">
-        <v>6537</v>
+        <v>123517</v>
       </c>
       <c r="S83" s="7"/>
       <c r="T83" s="7"/>
@@ -7241,7 +7260,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="3">
-        <v>2026080674</v>
+        <v>2026080912</v>
       </c>
       <c r="C84" s="3">
         <v>1</v>
@@ -7250,44 +7269,42 @@
         <v>29</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>136</v>
+        <v>293</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>163</v>
+        <v>66</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>108</v>
+        <v>321</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>325</v>
+        <v>273</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>326</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>260</v>
+        <v>327</v>
       </c>
       <c r="O84" s="3" t="s">
         <v>64</v>
       </c>
       <c r="P84" s="3"/>
-      <c r="Q84" s="3">
-        <v>49837</v>
-      </c>
+      <c r="Q84" s="3"/>
       <c r="R84" s="3">
-        <v>80692</v>
+        <v>1042</v>
       </c>
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
@@ -7311,7 +7328,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="7">
-        <v>2026080256</v>
+        <v>2026080915</v>
       </c>
       <c r="C85" s="7">
         <v>1</v>
@@ -7320,10 +7337,10 @@
         <v>29</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>106</v>
@@ -7332,22 +7349,22 @@
         <v>95</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="K85" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L85" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="M85" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="M85" s="8" t="s">
+      <c r="N85" s="8" t="s">
         <v>330</v>
-      </c>
-      <c r="N85" s="8" t="s">
-        <v>331</v>
       </c>
       <c r="O85" s="7" t="s">
         <v>64</v>
@@ -7355,7 +7372,7 @@
       <c r="P85" s="7"/>
       <c r="Q85" s="7"/>
       <c r="R85" s="7">
-        <v>47549</v>
+        <v>6537</v>
       </c>
       <c r="S85" s="7"/>
       <c r="T85" s="7"/>
@@ -7379,7 +7396,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="3">
-        <v>2026080063</v>
+        <v>2026080674</v>
       </c>
       <c r="C86" s="3">
         <v>1</v>
@@ -7388,42 +7405,44 @@
         <v>29</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>219</v>
+        <v>170</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>328</v>
+        <v>108</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>333</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>334</v>
+        <v>267</v>
       </c>
       <c r="O86" s="3" t="s">
         <v>64</v>
       </c>
       <c r="P86" s="3"/>
-      <c r="Q86" s="3"/>
+      <c r="Q86" s="3">
+        <v>49837</v>
+      </c>
       <c r="R86" s="3">
-        <v>23606</v>
+        <v>80692</v>
       </c>
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
@@ -7447,7 +7466,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="7">
-        <v>2026080064</v>
+        <v>2026080256</v>
       </c>
       <c r="C87" s="7">
         <v>1</v>
@@ -7456,66 +7475,66 @@
         <v>29</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>219</v>
+        <v>106</v>
       </c>
       <c r="H87" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="J87" s="7" t="s">
         <v>335</v>
-      </c>
-      <c r="I87" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>328</v>
       </c>
       <c r="K87" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="M87" s="8" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="N87" s="8" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="O87" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P87" s="7"/>
       <c r="Q87" s="7"/>
       <c r="R87" s="7">
-        <v>23606</v>
+        <v>47549</v>
       </c>
       <c r="S87" s="7"/>
       <c r="T87" s="7"/>
-      <c r="U87" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U87" s="7"/>
       <c r="V87" s="7"/>
       <c r="W87" s="7"/>
       <c r="X87" s="7"/>
       <c r="Y87" s="7"/>
       <c r="Z87" s="8" t="s">
-        <v>336</v>
+        <v>41</v>
       </c>
       <c r="AA87" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB87" s="7"/>
+      <c r="AB87" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:28">
       <c r="A88" s="3">
         <v>86</v>
       </c>
       <c r="B88" s="3">
-        <v>2026080060</v>
+        <v>2026080063</v>
       </c>
       <c r="C88" s="3">
         <v>1</v>
@@ -7524,34 +7543,34 @@
         <v>29</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>254</v>
+        <v>32</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="K88" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O88" s="3" t="s">
         <v>64</v>
@@ -7559,7 +7578,7 @@
       <c r="P88" s="3"/>
       <c r="Q88" s="3"/>
       <c r="R88" s="3">
-        <v>118283</v>
+        <v>23606</v>
       </c>
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
@@ -7583,7 +7602,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="7">
-        <v>2026080066</v>
+        <v>2026080064</v>
       </c>
       <c r="C89" s="7">
         <v>1</v>
@@ -7592,34 +7611,34 @@
         <v>29</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>98</v>
+        <v>226</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>188</v>
+        <v>342</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="K89" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M89" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N89" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="O89" s="7" t="s">
         <v>39</v>
@@ -7627,7 +7646,7 @@
       <c r="P89" s="7"/>
       <c r="Q89" s="7"/>
       <c r="R89" s="7">
-        <v>118283</v>
+        <v>23606</v>
       </c>
       <c r="S89" s="7"/>
       <c r="T89" s="7"/>
@@ -7639,21 +7658,19 @@
       <c r="X89" s="7"/>
       <c r="Y89" s="7"/>
       <c r="Z89" s="8" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="AA89" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB89" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB89" s="7"/>
     </row>
     <row r="90" spans="1:28">
       <c r="A90" s="3">
         <v>88</v>
       </c>
       <c r="B90" s="3">
-        <v>2026080111</v>
+        <v>2026080060</v>
       </c>
       <c r="C90" s="3">
         <v>1</v>
@@ -7662,34 +7679,34 @@
         <v>29</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>163</v>
+        <v>261</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>43</v>
+        <v>165</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="K90" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="O90" s="3" t="s">
         <v>64</v>
@@ -7697,7 +7714,7 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3">
-        <v>260202</v>
+        <v>118283</v>
       </c>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
@@ -7721,7 +7738,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="7">
-        <v>2026080131</v>
+        <v>2026080066</v>
       </c>
       <c r="C91" s="7">
         <v>1</v>
@@ -7730,34 +7747,34 @@
         <v>29</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>343</v>
+        <v>195</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="K91" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="N91" s="8" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="O91" s="7" t="s">
         <v>39</v>
@@ -7765,7 +7782,7 @@
       <c r="P91" s="7"/>
       <c r="Q91" s="7"/>
       <c r="R91" s="7">
-        <v>260202</v>
+        <v>118283</v>
       </c>
       <c r="S91" s="7"/>
       <c r="T91" s="7"/>
@@ -7777,19 +7794,21 @@
       <c r="X91" s="7"/>
       <c r="Y91" s="7"/>
       <c r="Z91" s="8" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="AA91" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB91" s="7"/>
+      <c r="AB91" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:28">
       <c r="A92" s="3">
         <v>90</v>
       </c>
       <c r="B92" s="3">
-        <v>2026080132</v>
+        <v>2026080111</v>
       </c>
       <c r="C92" s="3">
         <v>1</v>
@@ -7798,37 +7817,37 @@
         <v>29</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>343</v>
+        <v>170</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>344</v>
+        <v>43</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="K92" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P92" s="3"/>
       <c r="Q92" s="3"/>
@@ -7843,19 +7862,21 @@
       <c r="X92" s="3"/>
       <c r="Y92" s="3"/>
       <c r="Z92" s="6" t="s">
-        <v>345</v>
+        <v>41</v>
       </c>
       <c r="AA92" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB92" s="3"/>
+      <c r="AB92" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="93" spans="1:28">
       <c r="A93" s="7">
         <v>91</v>
       </c>
       <c r="B93" s="7">
-        <v>2026080061</v>
+        <v>2026080131</v>
       </c>
       <c r="C93" s="7">
         <v>1</v>
@@ -7864,66 +7885,66 @@
         <v>29</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>32</v>
+        <v>350</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="K93" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N93" s="8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O93" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P93" s="7"/>
       <c r="Q93" s="7"/>
       <c r="R93" s="7">
-        <v>191131</v>
+        <v>260202</v>
       </c>
       <c r="S93" s="7"/>
       <c r="T93" s="7"/>
-      <c r="U93" s="7"/>
+      <c r="U93" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="V93" s="7"/>
       <c r="W93" s="7"/>
       <c r="X93" s="7"/>
       <c r="Y93" s="7"/>
       <c r="Z93" s="8" t="s">
-        <v>41</v>
+        <v>343</v>
       </c>
       <c r="AA93" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB93" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB93" s="7"/>
     </row>
     <row r="94" spans="1:28">
       <c r="A94" s="3">
         <v>92</v>
       </c>
       <c r="B94" s="3">
-        <v>2026080065</v>
+        <v>2026080132</v>
       </c>
       <c r="C94" s="3">
         <v>1</v>
@@ -7932,68 +7953,64 @@
         <v>29</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G94" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J94" s="3" t="s">
         <v>335</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>328</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P94" s="3"/>
       <c r="Q94" s="3"/>
       <c r="R94" s="3">
-        <v>191131</v>
+        <v>260202</v>
       </c>
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
-      <c r="U94" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U94" s="3"/>
       <c r="V94" s="3"/>
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
       <c r="Y94" s="3"/>
       <c r="Z94" s="6" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB94" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB94" s="3"/>
     </row>
     <row r="95" spans="1:28">
       <c r="A95" s="7">
         <v>93</v>
       </c>
       <c r="B95" s="7">
-        <v>2026080458</v>
+        <v>2026080061</v>
       </c>
       <c r="C95" s="7">
         <v>1</v>
@@ -8002,42 +8019,42 @@
         <v>29</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>43</v>
+        <v>165</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>241</v>
+        <v>32</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>215</v>
+        <v>335</v>
       </c>
       <c r="K95" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>204</v>
+        <v>322</v>
       </c>
       <c r="M95" s="8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N95" s="8" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O95" s="7" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P95" s="7"/>
       <c r="Q95" s="7"/>
       <c r="R95" s="7">
-        <v>47584</v>
+        <v>191131</v>
       </c>
       <c r="S95" s="7"/>
       <c r="T95" s="7"/>
@@ -8047,7 +8064,7 @@
       <c r="X95" s="7"/>
       <c r="Y95" s="7"/>
       <c r="Z95" s="8" t="s">
-        <v>285</v>
+        <v>41</v>
       </c>
       <c r="AA95" s="7" t="s">
         <v>40</v>
@@ -8061,7 +8078,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="3">
-        <v>2026080457</v>
+        <v>2026080065</v>
       </c>
       <c r="C96" s="3">
         <v>1</v>
@@ -8070,52 +8087,54 @@
         <v>29</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>163</v>
+        <v>342</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>215</v>
+        <v>335</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>204</v>
+        <v>322</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
       <c r="R96" s="3">
-        <v>505328</v>
+        <v>191131</v>
       </c>
       <c r="S96" s="3"/>
       <c r="T96" s="3"/>
-      <c r="U96" s="3"/>
+      <c r="U96" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
       <c r="Y96" s="3"/>
       <c r="Z96" s="6" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="AA96" s="3" t="s">
         <v>40</v>
@@ -8129,7 +8148,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="7">
-        <v>2026080539</v>
+        <v>2026080458</v>
       </c>
       <c r="C97" s="7">
         <v>1</v>
@@ -8138,34 +8157,34 @@
         <v>29</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>241</v>
+        <v>43</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>58</v>
+        <v>248</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>126</v>
+        <v>222</v>
       </c>
       <c r="K97" s="7" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>119</v>
+        <v>211</v>
       </c>
       <c r="M97" s="8" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N97" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O97" s="7" t="s">
         <v>48</v>
@@ -8173,7 +8192,7 @@
       <c r="P97" s="7"/>
       <c r="Q97" s="7"/>
       <c r="R97" s="7">
-        <v>0</v>
+        <v>47584</v>
       </c>
       <c r="S97" s="7"/>
       <c r="T97" s="7"/>
@@ -8183,7 +8202,7 @@
       <c r="X97" s="7"/>
       <c r="Y97" s="7"/>
       <c r="Z97" s="8" t="s">
-        <v>358</v>
+        <v>292</v>
       </c>
       <c r="AA97" s="7" t="s">
         <v>40</v>
@@ -8197,7 +8216,7 @@
         <v>96</v>
       </c>
       <c r="B98" s="3">
-        <v>2026080991</v>
+        <v>2026080457</v>
       </c>
       <c r="C98" s="3">
         <v>1</v>
@@ -8206,50 +8225,52 @@
         <v>29</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>231</v>
+        <v>170</v>
       </c>
       <c r="H98" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I98" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="I98" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
+      <c r="J98" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L98" s="6" t="s">
-        <v>119</v>
+        <v>211</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>234</v>
+        <v>357</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>235</v>
+        <v>360</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
       <c r="R98" s="3">
-        <v>0</v>
+        <v>505328</v>
       </c>
       <c r="S98" s="3"/>
-      <c r="T98" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="3"/>
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
       <c r="Y98" s="3"/>
       <c r="Z98" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA98" s="3" t="s">
         <v>40</v>
@@ -8263,7 +8284,7 @@
         <v>97</v>
       </c>
       <c r="B99" s="7">
-        <v>2026080058</v>
+        <v>2026080539</v>
       </c>
       <c r="C99" s="7">
         <v>1</v>
@@ -8272,19 +8293,19 @@
         <v>29</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>32</v>
+        <v>248</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>219</v>
+        <v>58</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J99" s="7" t="s">
         <v>126</v>
@@ -8296,10 +8317,10 @@
         <v>119</v>
       </c>
       <c r="M99" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N99" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O99" s="7" t="s">
         <v>48</v>
@@ -8317,7 +8338,7 @@
       <c r="X99" s="7"/>
       <c r="Y99" s="7"/>
       <c r="Z99" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA99" s="7" t="s">
         <v>40</v>
@@ -8331,7 +8352,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="3">
-        <v>2026080239</v>
+        <v>2026080991</v>
       </c>
       <c r="C100" s="3">
         <v>1</v>
@@ -8340,19 +8361,19 @@
         <v>29</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>106</v>
+        <v>366</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>361</v>
+        <v>240</v>
       </c>
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
@@ -8360,10 +8381,10 @@
         <v>119</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>362</v>
+        <v>241</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>363</v>
+        <v>242</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>39</v>
@@ -8373,31 +8394,31 @@
       <c r="R100" s="3">
         <v>0</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="T100" s="3"/>
+      <c r="S100" s="3"/>
+      <c r="T100" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="U100" s="3"/>
       <c r="V100" s="3"/>
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
-      <c r="Y100" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y100" s="3"/>
       <c r="Z100" s="6" t="s">
-        <v>122</v>
+        <v>367</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB100" s="3"/>
+      <c r="AB100" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="101" spans="1:28">
       <c r="A101" s="7">
         <v>99</v>
       </c>
       <c r="B101" s="7">
-        <v>2026080059</v>
+        <v>2026080058</v>
       </c>
       <c r="C101" s="7">
         <v>1</v>
@@ -8406,19 +8427,19 @@
         <v>29</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>158</v>
+        <v>32</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>32</v>
+        <v>226</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J101" s="7" t="s">
         <v>126</v>
@@ -8430,10 +8451,10 @@
         <v>119</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="N101" s="8" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="O101" s="7" t="s">
         <v>48</v>
@@ -8451,7 +8472,7 @@
       <c r="X101" s="7"/>
       <c r="Y101" s="7"/>
       <c r="Z101" s="8" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="AA101" s="7" t="s">
         <v>40</v>
@@ -8465,7 +8486,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="3">
-        <v>2026080400</v>
+        <v>2026080239</v>
       </c>
       <c r="C102" s="3">
         <v>1</v>
@@ -8474,66 +8495,64 @@
         <v>29</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>65</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="H102" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I102" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>127</v>
-      </c>
+      <c r="J102" s="3"/>
+      <c r="K102" s="3"/>
       <c r="L102" s="6" t="s">
         <v>119</v>
       </c>
       <c r="M102" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="N102" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="N102" s="6" t="s">
-        <v>371</v>
-      </c>
       <c r="O102" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P102" s="3"/>
       <c r="Q102" s="3"/>
       <c r="R102" s="3">
         <v>0</v>
       </c>
-      <c r="S102" s="3"/>
+      <c r="S102" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T102" s="3"/>
       <c r="U102" s="3"/>
       <c r="V102" s="3"/>
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
-      <c r="Y102" s="3"/>
+      <c r="Y102" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z102" s="6" t="s">
-        <v>372</v>
+        <v>122</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB102" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB102" s="3"/>
     </row>
     <row r="103" spans="1:28">
       <c r="A103" s="7">
         <v>101</v>
       </c>
       <c r="B103" s="7">
-        <v>2026080406</v>
+        <v>2026080059</v>
       </c>
       <c r="C103" s="7">
         <v>1</v>
@@ -8542,90 +8561,226 @@
         <v>29</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>65</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>368</v>
+        <v>165</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>174</v>
+        <v>32</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="J103" s="7"/>
-      <c r="K103" s="7"/>
+        <v>372</v>
+      </c>
+      <c r="J103" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="K103" s="7" t="s">
+        <v>127</v>
+      </c>
       <c r="L103" s="8" t="s">
         <v>119</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="N103" s="8" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="O103" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P103" s="7"/>
       <c r="Q103" s="7"/>
       <c r="R103" s="7">
         <v>0</v>
       </c>
-      <c r="S103" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S103" s="7"/>
       <c r="T103" s="7"/>
       <c r="U103" s="7"/>
       <c r="V103" s="7"/>
       <c r="W103" s="7"/>
       <c r="X103" s="7"/>
-      <c r="Y103" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y103" s="7"/>
       <c r="Z103" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="AA103" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB103" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28">
+      <c r="A104" s="3">
+        <v>102</v>
+      </c>
+      <c r="B104" s="3">
+        <v>2026080400</v>
+      </c>
+      <c r="C104" s="3">
+        <v>1</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="J104" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="K104" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L104" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="N104" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="O104" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P104" s="3"/>
+      <c r="Q104" s="3"/>
+      <c r="R104" s="3">
+        <v>0</v>
+      </c>
+      <c r="S104" s="3"/>
+      <c r="T104" s="3"/>
+      <c r="U104" s="3"/>
+      <c r="V104" s="3"/>
+      <c r="W104" s="3"/>
+      <c r="X104" s="3"/>
+      <c r="Y104" s="3"/>
+      <c r="Z104" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="AA104" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB104" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28">
+      <c r="A105" s="7">
+        <v>103</v>
+      </c>
+      <c r="B105" s="7">
+        <v>2026080406</v>
+      </c>
+      <c r="C105" s="7">
+        <v>1</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="I105" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="J105" s="7"/>
+      <c r="K105" s="7"/>
+      <c r="L105" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="M105" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="N105" s="8" t="s">
+        <v>378</v>
+      </c>
+      <c r="O105" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P105" s="7"/>
+      <c r="Q105" s="7"/>
+      <c r="R105" s="7">
+        <v>0</v>
+      </c>
+      <c r="S105" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T105" s="7"/>
+      <c r="U105" s="7"/>
+      <c r="V105" s="7"/>
+      <c r="W105" s="7"/>
+      <c r="X105" s="7"/>
+      <c r="Y105" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z105" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="AA103" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB103" s="7"/>
-    </row>
-    <row r="104" spans="1:28">
-      <c r="A104" s="9"/>
-      <c r="B104" s="9"/>
-      <c r="C104" s="9"/>
-      <c r="D104" s="9"/>
-      <c r="E104" s="9"/>
-      <c r="F104" s="9"/>
-      <c r="G104" s="9"/>
-      <c r="H104" s="9"/>
-      <c r="I104" s="9"/>
-      <c r="J104" s="9"/>
-      <c r="K104" s="9"/>
-      <c r="L104" s="10"/>
-      <c r="M104" s="10"/>
-      <c r="N104" s="10"/>
-      <c r="O104" s="9"/>
-      <c r="P104" s="9"/>
-      <c r="Q104" s="9"/>
-      <c r="R104" s="9"/>
-      <c r="S104" s="9"/>
-      <c r="T104" s="9"/>
-      <c r="U104" s="9"/>
-      <c r="V104" s="9"/>
-      <c r="W104" s="9"/>
-      <c r="X104" s="9"/>
-      <c r="Y104" s="9"/>
-      <c r="Z104" s="10"/>
-      <c r="AA104" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="AB104" s="9">
-        <v>69</v>
+      <c r="AA105" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB105" s="7"/>
+    </row>
+    <row r="106" spans="1:28">
+      <c r="A106" s="9"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="9"/>
+      <c r="D106" s="9"/>
+      <c r="E106" s="9"/>
+      <c r="F106" s="9"/>
+      <c r="G106" s="9"/>
+      <c r="H106" s="9"/>
+      <c r="I106" s="9"/>
+      <c r="J106" s="9"/>
+      <c r="K106" s="9"/>
+      <c r="L106" s="10"/>
+      <c r="M106" s="10"/>
+      <c r="N106" s="10"/>
+      <c r="O106" s="9"/>
+      <c r="P106" s="9"/>
+      <c r="Q106" s="9"/>
+      <c r="R106" s="9"/>
+      <c r="S106" s="9"/>
+      <c r="T106" s="9"/>
+      <c r="U106" s="9"/>
+      <c r="V106" s="9"/>
+      <c r="W106" s="9"/>
+      <c r="X106" s="9"/>
+      <c r="Y106" s="9"/>
+      <c r="Z106" s="10"/>
+      <c r="AA106" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="AB106" s="9">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202608_Service_Count_Report.xlsx
+++ b/IM/202608_Service_Count_Report.xlsx
@@ -11,14 +11,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$106</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$AA$130</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="453">
   <si>
     <t>服務次數統計表        篩選月份：202608</t>
   </si>
@@ -272,6 +272,30 @@
     <t>新北市中和區新民街112號5樓-7</t>
   </si>
   <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>11:10:00</t>
+  </si>
+  <si>
+    <t>11:36:00</t>
+  </si>
+  <si>
+    <t>T301800166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">智基科技開發股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市永和區永和路2段57號6樓(永和分校)</t>
+  </si>
+  <si>
+    <t>永和</t>
+  </si>
+  <si>
+    <t>Pm 上熱要換</t>
+  </si>
+  <si>
     <t>14:30:00</t>
   </si>
   <si>
@@ -299,6 +323,18 @@
     <t>09:57:00</t>
   </si>
   <si>
+    <t>10:26:00</t>
+  </si>
+  <si>
+    <t>T302800120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">東南旅行社股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區和平街15-2號(中和分公司)</t>
+  </si>
+  <si>
     <t>11:24:00</t>
   </si>
   <si>
@@ -317,12 +353,6 @@
     <t>6F</t>
   </si>
   <si>
-    <t>11:10:00</t>
-  </si>
-  <si>
-    <t>11:36:00</t>
-  </si>
-  <si>
     <t>Pm 下次kt</t>
   </si>
   <si>
@@ -365,6 +395,39 @@
     <t>台北市士林區中山北路6段88號7樓</t>
   </si>
   <si>
+    <t>15:10:00</t>
+  </si>
+  <si>
+    <t>15:34:00</t>
+  </si>
+  <si>
+    <t>T352800006</t>
+  </si>
+  <si>
+    <t>eS-3528A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中原造像股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區建康路130號7樓-11</t>
+  </si>
+  <si>
+    <t>15:40:00</t>
+  </si>
+  <si>
+    <t>16:05:00</t>
+  </si>
+  <si>
+    <t>T352800007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中康彩色印刷事業股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市中和區建二路56號</t>
+  </si>
+  <si>
     <t>16:25:00</t>
   </si>
   <si>
@@ -440,6 +503,24 @@
     <t>三重洛陽店</t>
   </si>
   <si>
+    <t>14:08:00</t>
+  </si>
+  <si>
+    <t>THILF04573</t>
+  </si>
+  <si>
+    <t>新北市中和區工專路38號</t>
+  </si>
+  <si>
+    <t>中和浪漫店</t>
+  </si>
+  <si>
+    <t>14:54:00</t>
+  </si>
+  <si>
+    <t>清潔螢幕 重整排線 觸控校正</t>
+  </si>
+  <si>
     <t>13:00:00</t>
   </si>
   <si>
@@ -461,9 +542,6 @@
     <t>定位點跑掉，重新定位</t>
   </si>
   <si>
-    <t>15:10:00</t>
-  </si>
-  <si>
     <t>15:32:00</t>
   </si>
   <si>
@@ -482,6 +560,24 @@
     <t>檢查排線 重新校正</t>
   </si>
   <si>
+    <t>16:10:00</t>
+  </si>
+  <si>
+    <t>16:36:00</t>
+  </si>
+  <si>
+    <t>THILF0C742</t>
+  </si>
+  <si>
+    <t>新北市中和區景安路152號</t>
+  </si>
+  <si>
+    <t>中和景安站</t>
+  </si>
+  <si>
+    <t>清潔SiM卡 已請客服確認連線正常</t>
+  </si>
+  <si>
     <t>12:20:00</t>
   </si>
   <si>
@@ -581,9 +677,6 @@
     <t>T301800172</t>
   </si>
   <si>
-    <t xml:space="preserve">智基科技開發股份有限公司 </t>
-  </si>
-  <si>
     <t>新北市淡水區中山路123號3樓(淡水分校)</t>
   </si>
   <si>
@@ -677,13 +770,28 @@
     <t>新機裝機完成</t>
   </si>
   <si>
+    <t>17:23:00</t>
+  </si>
+  <si>
+    <t>17:28:00</t>
+  </si>
+  <si>
+    <t>T352500087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋐原能源股份有限公司 </t>
+  </si>
+  <si>
+    <t>桃園市蘆竹區機捷路二段646號1樓</t>
+  </si>
+  <si>
+    <t>蘆竹</t>
+  </si>
+  <si>
     <t>15:13:00</t>
   </si>
   <si>
     <t>T352500149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">東南旅行社股份有限公司 </t>
   </si>
   <si>
     <t>桃園市蘆竹區忠孝東路17之3號(南崁分公司</t>
@@ -777,6 +885,42 @@
     <t>淡水英才店</t>
   </si>
   <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
+    <t>THILF04739</t>
+  </si>
+  <si>
+    <t>新北市淡水區北新路二段17號</t>
+  </si>
+  <si>
+    <t>淡水櫻花店</t>
+  </si>
+  <si>
+    <t>改為緊急叫修，更換第一顆硬碟不備份還原</t>
+  </si>
+  <si>
+    <t>急修件</t>
+  </si>
+  <si>
+    <t>更換第一顆硬碟不備份還原</t>
+  </si>
+  <si>
+    <t>THILF04825</t>
+  </si>
+  <si>
+    <t>桃園市龜山區茶專路172巷2.4號</t>
+  </si>
+  <si>
+    <t>龜山兔子坑</t>
+  </si>
+  <si>
+    <t>重新啟動後可正常出單列印</t>
+  </si>
+  <si>
     <t>15:00:00</t>
   </si>
   <si>
@@ -808,6 +952,21 @@
     <t>湯家瑋</t>
   </si>
   <si>
+    <t>08:30:00</t>
+  </si>
+  <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>T251000051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">沛盈實業有限公司 </t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路665號9樓</t>
+  </si>
+  <si>
     <t>T252000086</t>
   </si>
   <si>
@@ -817,9 +976,6 @@
     <t>華固慕川</t>
   </si>
   <si>
-    <t>09:00:00</t>
-  </si>
-  <si>
     <t>T252000113</t>
   </si>
   <si>
@@ -844,7 +1000,19 @@
     <t>發票</t>
   </si>
   <si>
-    <t>08:30:00</t>
+    <t>T252000146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">台固媒體股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路657-12號8樓(新莊客服</t>
+  </si>
+  <si>
+    <t>新莊8F客服部</t>
+  </si>
+  <si>
+    <t>更換上熱</t>
   </si>
   <si>
     <t>08:50:00</t>
@@ -910,9 +1078,6 @@
     <t>三重湯城4樓(黑)J22</t>
   </si>
   <si>
-    <t>更換上熱</t>
-  </si>
-  <si>
     <t>09:50:00</t>
   </si>
   <si>
@@ -1009,6 +1174,15 @@
     <t>五股生鮮物流</t>
   </si>
   <si>
+    <t>T351800081</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路657-12號8樓(新莊客服部)</t>
+  </si>
+  <si>
+    <t>新莊8F</t>
+  </si>
+  <si>
     <t>T351800082</t>
   </si>
   <si>
@@ -1027,6 +1201,15 @@
     <t>節目部</t>
   </si>
   <si>
+    <t>T351800123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">優耐特精密機械股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市三重區興德路94號</t>
+  </si>
+  <si>
     <t>T352500148</t>
   </si>
   <si>
@@ -1039,9 +1222,6 @@
     <t>T352800011</t>
   </si>
   <si>
-    <t>eS-3528A 黑白複合機</t>
-  </si>
-  <si>
     <t xml:space="preserve">全聯實業股份有限公司 </t>
   </si>
   <si>
@@ -1100,6 +1280,24 @@
   </si>
   <si>
     <t>五股運輸</t>
+  </si>
+  <si>
+    <t>T451800006</t>
+  </si>
+  <si>
+    <t>eS-4518A 黑白複合機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">凱擘股份有限公司 </t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路657-10號2樓</t>
+  </si>
+  <si>
+    <t>T451800125</t>
+  </si>
+  <si>
+    <t>新北市新莊區中正路657-12號8樓(新莊8F)</t>
   </si>
   <si>
     <t>T452800031</t>
@@ -1134,12 +1332,24 @@
 換上8155006284</t>
   </si>
   <si>
+    <t>14:20:00</t>
+  </si>
+  <si>
+    <t>THILF03551</t>
+  </si>
+  <si>
+    <t>新北市板橋區永豐街51-1.51-2號一樓全部</t>
+  </si>
+  <si>
+    <t>板橋板豐店</t>
+  </si>
+  <si>
+    <t>撤店</t>
+  </si>
+  <si>
     <t>15:20:00</t>
   </si>
   <si>
-    <t>撤店</t>
-  </si>
-  <si>
     <t>THILF03892</t>
   </si>
   <si>
@@ -1174,6 +1384,12 @@
   </si>
   <si>
     <t>清潔切刀</t>
+  </si>
+  <si>
+    <t>狄澤洋</t>
+  </si>
+  <si>
+    <t>裝潢撤機已完工</t>
   </si>
   <si>
     <t>合計</t>
@@ -1590,7 +1806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB106"/>
+  <dimension ref="A1:AB130"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -2372,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026080119</v>
+        <v>2026081085</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -2384,19 +2600,19 @@
         <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>36</v>
@@ -2411,21 +2627,25 @@
         <v>86</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3">
-        <v>84954</v>
-      </c>
-      <c r="S12" s="3"/>
+        <v>49104</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
-      <c r="Z12" s="6"/>
+      <c r="Z12" s="6" t="s">
+        <v>87</v>
+      </c>
       <c r="AA12" s="3" t="s">
         <v>40</v>
       </c>
@@ -2438,7 +2658,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026080564</v>
+        <v>2026081086</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -2450,19 +2670,19 @@
         <v>30</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>36</v>
@@ -2477,16 +2697,14 @@
         <v>86</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7">
-        <v>84960</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>49104</v>
+      </c>
+      <c r="S13" s="7"/>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
@@ -2494,21 +2712,19 @@
       <c r="X13" s="7"/>
       <c r="Y13" s="7"/>
       <c r="Z13" s="8" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="AA13" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB13" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB13" s="7"/>
     </row>
     <row r="14" spans="1:28">
       <c r="A14" s="3">
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026080403</v>
+        <v>2026080119</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -2520,19 +2736,19 @@
         <v>30</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>36</v>
@@ -2547,25 +2763,21 @@
         <v>94</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3">
-        <v>39573</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>84954</v>
+      </c>
+      <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
-      <c r="Z14" s="6" t="s">
-        <v>41</v>
-      </c>
+      <c r="Z14" s="6"/>
       <c r="AA14" s="3" t="s">
         <v>40</v>
       </c>
@@ -2578,7 +2790,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7">
-        <v>2026080933</v>
+        <v>2026080564</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -2590,7 +2802,7 @@
         <v>30</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>95</v>
@@ -2599,10 +2811,10 @@
         <v>96</v>
       </c>
       <c r="I15" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>36</v>
@@ -2622,7 +2834,7 @@
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7">
-        <v>40735</v>
+        <v>84960</v>
       </c>
       <c r="S15" s="7" t="s">
         <v>40</v>
@@ -2634,7 +2846,7 @@
       <c r="X15" s="7"/>
       <c r="Y15" s="7"/>
       <c r="Z15" s="8" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="AA15" s="7" t="s">
         <v>40</v>
@@ -2648,7 +2860,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="3">
-        <v>2026080934</v>
+        <v>2026081079</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -2660,41 +2872,43 @@
         <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3">
-        <v>40735</v>
-      </c>
-      <c r="S16" s="3"/>
+        <v>57965</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
@@ -2702,19 +2916,21 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="6" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="AA16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB16" s="3"/>
+      <c r="AB16" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:28">
       <c r="A17" s="7">
         <v>15</v>
       </c>
       <c r="B17" s="7">
-        <v>2026080402</v>
+        <v>2026080403</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -2729,28 +2945,28 @@
         <v>65</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O17" s="7" t="s">
         <v>39</v>
@@ -2758,7 +2974,7 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7">
-        <v>5308</v>
+        <v>39573</v>
       </c>
       <c r="S17" s="7" t="s">
         <v>40</v>
@@ -2784,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="3">
-        <v>2026080905</v>
+        <v>2026080933</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -2799,28 +3015,28 @@
         <v>31</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>39</v>
@@ -2828,7 +3044,7 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3">
-        <v>11858</v>
+        <v>40735</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>40</v>
@@ -2840,7 +3056,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
       <c r="Z18" s="6" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>40</v>
@@ -2854,7 +3070,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="7">
-        <v>2026080906</v>
+        <v>2026080934</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2869,28 +3085,28 @@
         <v>31</v>
       </c>
       <c r="G19" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>100</v>
-      </c>
       <c r="J19" s="7" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="O19" s="7" t="s">
         <v>64</v>
@@ -2898,7 +3114,7 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7">
-        <v>11858</v>
+        <v>40735</v>
       </c>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -2908,7 +3124,7 @@
       <c r="X19" s="7"/>
       <c r="Y19" s="7"/>
       <c r="Z19" s="8" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="AA19" s="7" t="s">
         <v>40</v>
@@ -2920,7 +3136,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="3">
-        <v>2026080567</v>
+        <v>2026080402</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -2932,39 +3148,39 @@
         <v>30</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="N20" s="6"/>
+        <v>111</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="O20" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P20" s="3"/>
-      <c r="Q20" s="3">
-        <v>3330</v>
-      </c>
+      <c r="Q20" s="3"/>
       <c r="R20" s="3">
-        <v>36588</v>
+        <v>5308</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>40</v>
@@ -2990,7 +3206,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="7">
-        <v>2026080760</v>
+        <v>2026080905</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -3002,41 +3218,43 @@
         <v>30</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="N21" s="8"/>
+        <v>111</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>112</v>
+      </c>
       <c r="O21" s="7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="P21" s="7"/>
-      <c r="Q21" s="7">
-        <v>29691</v>
-      </c>
+      <c r="Q21" s="7"/>
       <c r="R21" s="7">
-        <v>831562</v>
-      </c>
-      <c r="S21" s="7"/>
+        <v>11858</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T21" s="7"/>
       <c r="U21" s="7"/>
       <c r="V21" s="7"/>
@@ -3044,7 +3262,7 @@
       <c r="X21" s="7"/>
       <c r="Y21" s="7"/>
       <c r="Z21" s="8" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="AA21" s="7" t="s">
         <v>40</v>
@@ -3058,7 +3276,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="3">
-        <v>2026080761</v>
+        <v>2026080906</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -3070,43 +3288,41 @@
         <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N22" s="6"/>
+        <v>111</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="O22" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P22" s="3"/>
-      <c r="Q22" s="3">
-        <v>29691</v>
-      </c>
+      <c r="Q22" s="3"/>
       <c r="R22" s="3">
-        <v>831722</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>11858</v>
+      </c>
+      <c r="S22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
@@ -3126,7 +3342,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="7">
-        <v>2026080762</v>
+        <v>2026080567</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -3141,38 +3357,40 @@
         <v>42</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="N23" s="8"/>
       <c r="O23" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P23" s="7"/>
       <c r="Q23" s="7">
-        <v>29691</v>
+        <v>3330</v>
       </c>
       <c r="R23" s="7">
-        <v>831722</v>
-      </c>
-      <c r="S23" s="7"/>
+        <v>36588</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T23" s="7"/>
       <c r="U23" s="7"/>
       <c r="V23" s="7"/>
@@ -3185,14 +3403,16 @@
       <c r="AA23" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB23" s="7"/>
+      <c r="AB23" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:28">
       <c r="A24" s="3">
         <v>22</v>
       </c>
       <c r="B24" s="3">
-        <v>2026080438</v>
+        <v>2026081119</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -3204,35 +3424,37 @@
         <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
+        <v>123</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L24" s="6" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>121</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="N24" s="6"/>
       <c r="O24" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>160525</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>40</v>
@@ -3242,11 +3464,9 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
-      <c r="Y24" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y24" s="3"/>
       <c r="Z24" s="6" t="s">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>40</v>
@@ -3260,7 +3480,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="7">
-        <v>2026080793</v>
+        <v>2026081120</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -3272,39 +3492,37 @@
         <v>30</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G25" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="J25" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="K25" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="J25" s="7" t="s">
+      <c r="M25" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="K25" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="N25" s="8" t="s">
-        <v>129</v>
-      </c>
+      <c r="N25" s="8"/>
       <c r="O25" s="7" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7">
-        <v>0</v>
+        <v>160525</v>
       </c>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -3314,21 +3532,19 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8" t="s">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="AA25" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB25" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB25" s="7"/>
     </row>
     <row r="26" spans="1:28">
       <c r="A26" s="3">
         <v>24</v>
       </c>
       <c r="B26" s="3">
-        <v>2026080451</v>
+        <v>2026081144</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -3340,35 +3556,37 @@
         <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M26" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>135</v>
-      </c>
+      <c r="N26" s="6"/>
       <c r="O26" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3">
-        <v>0</v>
+        <v>285406</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>40</v>
@@ -3378,11 +3596,9 @@
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
-      <c r="Y26" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y26" s="3"/>
       <c r="Z26" s="6" t="s">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>40</v>
@@ -3396,7 +3612,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="7">
-        <v>2026080411</v>
+        <v>2026081145</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -3408,63 +3624,59 @@
         <v>30</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
+        <v>129</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L27" s="8" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="N27" s="8" t="s">
-        <v>140</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="N27" s="8"/>
       <c r="O27" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
       <c r="R27" s="7">
-        <v>0</v>
-      </c>
-      <c r="S27" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>285406</v>
+      </c>
+      <c r="S27" s="7"/>
       <c r="T27" s="7"/>
       <c r="U27" s="7"/>
       <c r="V27" s="7"/>
       <c r="W27" s="7"/>
       <c r="X27" s="7"/>
-      <c r="Y27" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y27" s="7"/>
       <c r="Z27" s="8" t="s">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="AA27" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB27" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB27" s="7"/>
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="3">
         <v>26</v>
       </c>
       <c r="B28" s="3">
-        <v>2026080127</v>
+        <v>2026080760</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -3476,39 +3688,39 @@
         <v>30</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>140</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="N28" s="6"/>
       <c r="O28" s="3" t="s">
         <v>48</v>
       </c>
       <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
+      <c r="Q28" s="3">
+        <v>29691</v>
+      </c>
       <c r="R28" s="3">
-        <v>0</v>
+        <v>831562</v>
       </c>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
@@ -3518,19 +3730,21 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="6" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AA28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB28" s="3"/>
+      <c r="AB28" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:28">
       <c r="A29" s="7">
         <v>27</v>
       </c>
       <c r="B29" s="7">
-        <v>2026080999</v>
+        <v>2026080761</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -3542,35 +3756,39 @@
         <v>30</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>143</v>
+        <v>75</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
+        <v>133</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L29" s="8" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="N29" s="8" t="s">
-        <v>147</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="N29" s="8"/>
       <c r="O29" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
+      <c r="Q29" s="7">
+        <v>29691</v>
+      </c>
       <c r="R29" s="7">
-        <v>0</v>
+        <v>831722</v>
       </c>
       <c r="S29" s="7" t="s">
         <v>40</v>
@@ -3580,25 +3798,21 @@
       <c r="V29" s="7"/>
       <c r="W29" s="7"/>
       <c r="X29" s="7"/>
-      <c r="Y29" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y29" s="7"/>
       <c r="Z29" s="8" t="s">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="AA29" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB29" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB29" s="7"/>
     </row>
     <row r="30" spans="1:28">
       <c r="A30" s="3">
         <v>28</v>
       </c>
       <c r="B30" s="3">
-        <v>2026080946</v>
+        <v>2026080762</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -3610,39 +3824,39 @@
         <v>30</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>144</v>
+        <v>75</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>147</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="N30" s="6"/>
       <c r="O30" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
+      <c r="Q30" s="3">
+        <v>29691</v>
+      </c>
       <c r="R30" s="3">
-        <v>0</v>
+        <v>831722</v>
       </c>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
@@ -3652,7 +3866,7 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
       <c r="Z30" s="6" t="s">
-        <v>149</v>
+        <v>41</v>
       </c>
       <c r="AA30" s="3" t="s">
         <v>40</v>
@@ -3664,7 +3878,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="7">
-        <v>2026080090</v>
+        <v>2026080438</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -3676,27 +3890,27 @@
         <v>30</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
       <c r="L31" s="8" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>39</v>
@@ -3718,7 +3932,7 @@
         <v>40</v>
       </c>
       <c r="Z31" s="8" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="AA31" s="7" t="s">
         <v>40</v>
@@ -3732,7 +3946,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="3">
-        <v>2026080005</v>
+        <v>2026080793</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3744,31 +3958,31 @@
         <v>30</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>48</v>
@@ -3786,19 +4000,21 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB32" s="3"/>
+      <c r="AB32" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:28">
       <c r="A33" s="7">
         <v>31</v>
       </c>
       <c r="B33" s="7">
-        <v>2026080224</v>
+        <v>2026080451</v>
       </c>
       <c r="C33" s="7">
         <v>1</v>
@@ -3813,28 +4029,24 @@
         <v>65</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
       <c r="L33" s="8" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="O33" s="7" t="s">
         <v>39</v>
@@ -3842,7 +4054,7 @@
       <c r="P33" s="7"/>
       <c r="Q33" s="7"/>
       <c r="R33" s="7">
-        <v>2688</v>
+        <v>0</v>
       </c>
       <c r="S33" s="7" t="s">
         <v>40</v>
@@ -3852,9 +4064,11 @@
       <c r="V33" s="7"/>
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
-      <c r="Y33" s="7"/>
+      <c r="Y33" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z33" s="8" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="AA33" s="7" t="s">
         <v>40</v>
@@ -3868,7 +4082,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="3">
-        <v>2026080936</v>
+        <v>2026081099</v>
       </c>
       <c r="C34" s="3">
         <v>1</v>
@@ -3877,46 +4091,38 @@
         <v>29</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
       <c r="L34" s="6" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P34" s="3">
-        <v>8160</v>
-      </c>
-      <c r="Q34" s="3">
-        <v>17940</v>
-      </c>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
       <c r="R34" s="3">
-        <v>26200</v>
+        <v>0</v>
       </c>
       <c r="S34" s="3" t="s">
         <v>40</v>
@@ -3926,9 +4132,11 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
+      <c r="Y34" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z34" s="6" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="AA34" s="3" t="s">
         <v>40</v>
@@ -3942,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="7">
-        <v>2026080937</v>
+        <v>2026081002</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -3951,46 +4159,42 @@
         <v>29</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>32</v>
+        <v>161</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>37</v>
+        <v>140</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="P35" s="7">
-        <v>8160</v>
-      </c>
-      <c r="Q35" s="7">
-        <v>17940</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
       <c r="R35" s="7">
-        <v>26200</v>
+        <v>0</v>
       </c>
       <c r="S35" s="7"/>
       <c r="T35" s="7"/>
@@ -4000,7 +4204,7 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="AA35" s="7" t="s">
         <v>40</v>
@@ -4012,7 +4216,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="3">
-        <v>2026080115</v>
+        <v>2026080411</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -4021,44 +4225,38 @@
         <v>29</v>
       </c>
       <c r="E36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="I36" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
       <c r="L36" s="6" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="O36" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P36" s="3"/>
-      <c r="Q36" s="3">
-        <v>2754</v>
-      </c>
+      <c r="Q36" s="3"/>
       <c r="R36" s="3">
-        <v>153369</v>
+        <v>0</v>
       </c>
       <c r="S36" s="3" t="s">
         <v>40</v>
@@ -4068,19 +4266,25 @@
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
       <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
+      <c r="Y36" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z36" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA36" s="3"/>
-      <c r="AB36" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="AA36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:28">
       <c r="A37" s="7">
         <v>35</v>
       </c>
       <c r="B37" s="7">
-        <v>2026080116</v>
+        <v>2026080127</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -4089,44 +4293,42 @@
         <v>29</v>
       </c>
       <c r="E37" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G37" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>170</v>
-      </c>
       <c r="H37" s="7" t="s">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="M37" s="8" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="P37" s="7"/>
-      <c r="Q37" s="7">
-        <v>2754</v>
-      </c>
+      <c r="Q37" s="7"/>
       <c r="R37" s="7">
-        <v>153369</v>
+        <v>0</v>
       </c>
       <c r="S37" s="7"/>
       <c r="T37" s="7"/>
@@ -4138,7 +4340,9 @@
       <c r="Z37" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="AA37" s="7"/>
+      <c r="AA37" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB37" s="7"/>
     </row>
     <row r="38" spans="1:28">
@@ -4146,7 +4350,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="3">
-        <v>2026080128</v>
+        <v>2026080999</v>
       </c>
       <c r="C38" s="3">
         <v>1</v>
@@ -4155,42 +4359,38 @@
         <v>29</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
       <c r="L38" s="6" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="N38" s="6"/>
+        <v>172</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>173</v>
+      </c>
       <c r="O38" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P38" s="3"/>
-      <c r="Q38" s="3">
-        <v>636</v>
-      </c>
+      <c r="Q38" s="3"/>
       <c r="R38" s="3">
-        <v>26641</v>
+        <v>0</v>
       </c>
       <c r="S38" s="3" t="s">
         <v>40</v>
@@ -4200,9 +4400,11 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
       <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
+      <c r="Y38" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="Z38" s="6" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="AA38" s="3" t="s">
         <v>40</v>
@@ -4216,7 +4418,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="7">
-        <v>2026080129</v>
+        <v>2026080946</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -4225,42 +4427,42 @@
         <v>29</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="N39" s="8"/>
+        <v>172</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="O39" s="7" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="P39" s="7"/>
-      <c r="Q39" s="7">
-        <v>636</v>
-      </c>
+      <c r="Q39" s="7"/>
       <c r="R39" s="7">
-        <v>26641</v>
+        <v>0</v>
       </c>
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
@@ -4270,7 +4472,7 @@
       <c r="X39" s="7"/>
       <c r="Y39" s="7"/>
       <c r="Z39" s="8" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AA39" s="7" t="s">
         <v>40</v>
@@ -4282,7 +4484,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3">
-        <v>2026080653</v>
+        <v>2026080791</v>
       </c>
       <c r="C40" s="3">
         <v>1</v>
@@ -4291,46 +4493,44 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G40" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="N40" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L40" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="M40" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="N40" s="6" t="s">
-        <v>185</v>
-      </c>
       <c r="O40" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3">
-        <v>30354</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
@@ -4338,7 +4538,7 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="6" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AA40" s="3" t="s">
         <v>40</v>
@@ -4352,7 +4552,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="7">
-        <v>2026080654</v>
+        <v>2026080090</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -4361,64 +4561,66 @@
         <v>29</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
       <c r="L41" s="8" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N41" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P41" s="7"/>
       <c r="Q41" s="7"/>
       <c r="R41" s="7">
-        <v>30354</v>
-      </c>
-      <c r="S41" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T41" s="7"/>
       <c r="U41" s="7"/>
       <c r="V41" s="7"/>
       <c r="W41" s="7"/>
       <c r="X41" s="7"/>
-      <c r="Y41" s="7"/>
+      <c r="Y41" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="Z41" s="8" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="AA41" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB41" s="7"/>
+      <c r="AB41" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:28">
       <c r="A42" s="3">
         <v>40</v>
       </c>
       <c r="B42" s="3">
-        <v>2026080571</v>
+        <v>2026080005</v>
       </c>
       <c r="C42" s="3">
         <v>1</v>
@@ -4427,66 +4629,64 @@
         <v>29</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="N42" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="N42" s="6"/>
       <c r="O42" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3">
-        <v>53103</v>
+        <v>0</v>
       </c>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
-      <c r="U42" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB42" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB42" s="3"/>
     </row>
     <row r="43" spans="1:28">
       <c r="A43" s="7">
         <v>41</v>
       </c>
       <c r="B43" s="7">
-        <v>2026080623</v>
+        <v>2026080224</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -4495,22 +4695,22 @@
         <v>29</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>123</v>
+        <v>189</v>
       </c>
       <c r="H43" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="I43" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="J43" s="7" t="s">
         <v>192</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>36</v>
@@ -4521,16 +4721,20 @@
       <c r="M43" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="N43" s="8"/>
+      <c r="N43" s="8" t="s">
+        <v>195</v>
+      </c>
       <c r="O43" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P43" s="7"/>
       <c r="Q43" s="7"/>
       <c r="R43" s="7">
-        <v>38400</v>
-      </c>
-      <c r="S43" s="7"/>
+        <v>2688</v>
+      </c>
+      <c r="S43" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
       <c r="V43" s="7"/>
@@ -4538,7 +4742,7 @@
       <c r="X43" s="7"/>
       <c r="Y43" s="7"/>
       <c r="Z43" s="8" t="s">
-        <v>169</v>
+        <v>41</v>
       </c>
       <c r="AA43" s="7" t="s">
         <v>40</v>
@@ -4552,7 +4756,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="3">
-        <v>2026080077</v>
+        <v>2026080936</v>
       </c>
       <c r="C44" s="3">
         <v>1</v>
@@ -4561,64 +4765,72 @@
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>197</v>
+        <v>37</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3"/>
+      <c r="P44" s="3">
+        <v>8160</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>17940</v>
+      </c>
       <c r="R44" s="3">
-        <v>125866</v>
-      </c>
-      <c r="S44" s="3"/>
+        <v>26200</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T44" s="3"/>
-      <c r="U44" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="AA44" s="3"/>
-      <c r="AB44" s="3"/>
+        <v>201</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:28">
       <c r="A45" s="7">
         <v>43</v>
       </c>
       <c r="B45" s="7">
-        <v>2026080075</v>
+        <v>2026080937</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -4627,46 +4839,48 @@
         <v>29</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>201</v>
+        <v>32</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>197</v>
+        <v>37</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N45" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O45" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P45" s="7"/>
-      <c r="Q45" s="7"/>
+        <v>64</v>
+      </c>
+      <c r="P45" s="7">
+        <v>8160</v>
+      </c>
+      <c r="Q45" s="7">
+        <v>17940</v>
+      </c>
       <c r="R45" s="7">
-        <v>135251</v>
-      </c>
-      <c r="S45" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>26200</v>
+      </c>
+      <c r="S45" s="7"/>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
       <c r="V45" s="7"/>
@@ -4674,9 +4888,11 @@
       <c r="X45" s="7"/>
       <c r="Y45" s="7"/>
       <c r="Z45" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA45" s="7"/>
+        <v>201</v>
+      </c>
+      <c r="AA45" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="AB45" s="7"/>
     </row>
     <row r="46" spans="1:28">
@@ -4684,7 +4900,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="3">
-        <v>2026080076</v>
+        <v>2026080115</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -4693,44 +4909,48 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>201</v>
+        <v>43</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
+      <c r="Q46" s="3">
+        <v>2754</v>
+      </c>
       <c r="R46" s="3">
-        <v>135251</v>
-      </c>
-      <c r="S46" s="3"/>
+        <v>153369</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
@@ -4738,7 +4958,7 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="6" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
@@ -4748,7 +4968,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="7">
-        <v>2026080073</v>
+        <v>2026080116</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -4757,46 +4977,46 @@
         <v>29</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>200</v>
+        <v>43</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="K47" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L47" s="8" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
+      <c r="Q47" s="7">
+        <v>2754</v>
+      </c>
       <c r="R47" s="7">
-        <v>6329</v>
-      </c>
-      <c r="S47" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>153369</v>
+      </c>
+      <c r="S47" s="7"/>
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
       <c r="V47" s="7"/>
@@ -4804,7 +5024,7 @@
       <c r="X47" s="7"/>
       <c r="Y47" s="7"/>
       <c r="Z47" s="8" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="AA47" s="7"/>
       <c r="AB47" s="7"/>
@@ -4814,7 +5034,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="3">
-        <v>2026080074</v>
+        <v>2026080128</v>
       </c>
       <c r="C48" s="3">
         <v>1</v>
@@ -4823,44 +5043,46 @@
         <v>29</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>50</v>
+        <v>207</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>199</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N48" s="6"/>
       <c r="O48" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
+      <c r="Q48" s="3">
+        <v>636</v>
+      </c>
       <c r="R48" s="3">
-        <v>6329</v>
-      </c>
-      <c r="S48" s="3"/>
+        <v>26641</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T48" s="3"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
@@ -4868,17 +5090,21 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA48" s="3"/>
-      <c r="AB48" s="3"/>
+        <v>201</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB48" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" spans="1:28">
       <c r="A49" s="7">
         <v>47</v>
       </c>
       <c r="B49" s="7">
-        <v>2026080629</v>
+        <v>2026080129</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -4887,48 +5113,44 @@
         <v>29</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>206</v>
+        <v>53</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="N49" s="8" t="s">
-        <v>185</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N49" s="8"/>
       <c r="O49" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P49" s="7"/>
       <c r="Q49" s="7">
-        <v>3160</v>
+        <v>636</v>
       </c>
       <c r="R49" s="7">
-        <v>415812</v>
-      </c>
-      <c r="S49" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>26641</v>
+      </c>
+      <c r="S49" s="7"/>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
       <c r="V49" s="7"/>
@@ -4936,21 +5158,19 @@
       <c r="X49" s="7"/>
       <c r="Y49" s="7"/>
       <c r="Z49" s="8" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="AA49" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB49" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB49" s="7"/>
     </row>
     <row r="50" spans="1:28">
       <c r="A50" s="3">
         <v>48</v>
       </c>
       <c r="B50" s="3">
-        <v>2026080630</v>
+        <v>2026080653</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -4959,46 +5179,46 @@
         <v>29</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>206</v>
+        <v>77</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>207</v>
+        <v>84</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="O50" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P50" s="3"/>
-      <c r="Q50" s="3">
-        <v>3160</v>
-      </c>
+      <c r="Q50" s="3"/>
       <c r="R50" s="3">
-        <v>415812</v>
-      </c>
-      <c r="S50" s="3"/>
+        <v>30354</v>
+      </c>
+      <c r="S50" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
@@ -5006,19 +5226,21 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="6" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="AA50" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB50" s="3"/>
+      <c r="AB50" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:28">
       <c r="A51" s="7">
         <v>49</v>
       </c>
       <c r="B51" s="7">
-        <v>2026080408</v>
+        <v>2026080654</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -5027,68 +5249,64 @@
         <v>29</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>206</v>
+        <v>77</v>
       </c>
       <c r="K51" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>211</v>
+        <v>84</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="N51" s="8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="O51" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P51" s="7"/>
       <c r="Q51" s="7"/>
       <c r="R51" s="7">
-        <v>0</v>
+        <v>30354</v>
       </c>
       <c r="S51" s="7"/>
-      <c r="T51" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="T51" s="7"/>
       <c r="U51" s="7"/>
       <c r="V51" s="7"/>
       <c r="W51" s="7"/>
       <c r="X51" s="7"/>
       <c r="Y51" s="7"/>
       <c r="Z51" s="8" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AA51" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB51" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB51" s="7"/>
     </row>
     <row r="52" spans="1:28">
       <c r="A52" s="3">
         <v>50</v>
       </c>
       <c r="B52" s="3">
-        <v>2026080440</v>
+        <v>2026080571</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -5097,66 +5315,66 @@
         <v>29</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="N52" s="6" t="s">
-        <v>219</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N52" s="6"/>
       <c r="O52" s="3" t="s">
         <v>39</v>
       </c>
       <c r="P52" s="3"/>
-      <c r="Q52" s="3">
-        <v>7167</v>
-      </c>
+      <c r="Q52" s="3"/>
       <c r="R52" s="3">
-        <v>39533</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>53103</v>
+      </c>
+      <c r="S52" s="3"/>
       <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
+      <c r="U52" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA52" s="3"/>
-      <c r="AB52" s="3"/>
+        <v>221</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:28">
       <c r="A53" s="7">
         <v>51</v>
       </c>
       <c r="B53" s="7">
-        <v>2026080441</v>
+        <v>2026080623</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -5165,44 +5383,40 @@
         <v>29</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L53" s="8" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="N53" s="8" t="s">
-        <v>219</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N53" s="8"/>
       <c r="O53" s="7" t="s">
         <v>64</v>
       </c>
       <c r="P53" s="7"/>
-      <c r="Q53" s="7">
-        <v>7167</v>
-      </c>
+      <c r="Q53" s="7"/>
       <c r="R53" s="7">
-        <v>39533</v>
+        <v>38400</v>
       </c>
       <c r="S53" s="7"/>
       <c r="T53" s="7"/>
@@ -5212,17 +5426,21 @@
       <c r="X53" s="7"/>
       <c r="Y53" s="7"/>
       <c r="Z53" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA53" s="7"/>
-      <c r="AB53" s="7"/>
+        <v>201</v>
+      </c>
+      <c r="AA53" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB53" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:28">
       <c r="A54" s="3">
         <v>52</v>
       </c>
       <c r="B54" s="3">
-        <v>2026080112</v>
+        <v>2026080077</v>
       </c>
       <c r="C54" s="3">
         <v>1</v>
@@ -5231,34 +5449,34 @@
         <v>29</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>57</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>220</v>
+        <v>50</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>39</v>
@@ -5266,11 +5484,9 @@
       <c r="P54" s="3"/>
       <c r="Q54" s="3"/>
       <c r="R54" s="3">
-        <v>251357</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>125866</v>
+      </c>
+      <c r="S54" s="3"/>
       <c r="T54" s="3"/>
       <c r="U54" s="3" t="s">
         <v>40</v>
@@ -5280,7 +5496,7 @@
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AA54" s="3"/>
       <c r="AB54" s="3"/>
@@ -5290,7 +5506,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="7">
-        <v>2026080113</v>
+        <v>2026080075</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -5299,44 +5515,46 @@
         <v>29</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>43</v>
+        <v>231</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>172</v>
+        <v>228</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="N55" s="8" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="O55" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P55" s="7"/>
       <c r="Q55" s="7"/>
       <c r="R55" s="7">
-        <v>251357</v>
-      </c>
-      <c r="S55" s="7"/>
+        <v>135251</v>
+      </c>
+      <c r="S55" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
       <c r="V55" s="7"/>
@@ -5344,7 +5562,7 @@
       <c r="X55" s="7"/>
       <c r="Y55" s="7"/>
       <c r="Z55" s="8" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="AA55" s="7"/>
       <c r="AB55" s="7"/>
@@ -5354,7 +5572,7 @@
         <v>54</v>
       </c>
       <c r="B56" s="3">
-        <v>2026080939</v>
+        <v>2026080076</v>
       </c>
       <c r="C56" s="3">
         <v>1</v>
@@ -5363,22 +5581,22 @@
         <v>29</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>98</v>
+        <v>232</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>227</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>36</v>
@@ -5396,11 +5614,9 @@
         <v>64</v>
       </c>
       <c r="P56" s="3"/>
-      <c r="Q56" s="3">
-        <v>3815</v>
-      </c>
+      <c r="Q56" s="3"/>
       <c r="R56" s="3">
-        <v>225709</v>
+        <v>135251</v>
       </c>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
@@ -5410,7 +5626,7 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="6" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
@@ -5420,7 +5636,7 @@
         <v>55</v>
       </c>
       <c r="B57" s="7">
-        <v>2026080938</v>
+        <v>2026080073</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -5429,22 +5645,22 @@
         <v>29</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>226</v>
+        <v>50</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>98</v>
+        <v>231</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="J57" s="7" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="K57" s="7" t="s">
         <v>36</v>
@@ -5462,11 +5678,9 @@
         <v>39</v>
       </c>
       <c r="P57" s="7"/>
-      <c r="Q57" s="7">
-        <v>3815</v>
-      </c>
+      <c r="Q57" s="7"/>
       <c r="R57" s="7">
-        <v>225709</v>
+        <v>6329</v>
       </c>
       <c r="S57" s="7" t="s">
         <v>40</v>
@@ -5478,7 +5692,7 @@
       <c r="X57" s="7"/>
       <c r="Y57" s="7"/>
       <c r="Z57" s="8" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="AA57" s="7"/>
       <c r="AB57" s="7"/>
@@ -5488,7 +5702,7 @@
         <v>56</v>
       </c>
       <c r="B58" s="3">
-        <v>2026080940</v>
+        <v>2026080074</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -5497,22 +5711,22 @@
         <v>29</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>231</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>36</v>
@@ -5524,21 +5738,17 @@
         <v>229</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="O58" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P58" s="3"/>
-      <c r="Q58" s="3">
-        <v>11287</v>
-      </c>
+      <c r="Q58" s="3"/>
       <c r="R58" s="3">
-        <v>310496</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>6329</v>
+      </c>
+      <c r="S58" s="3"/>
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
@@ -5546,7 +5756,7 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="6" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="AA58" s="3"/>
       <c r="AB58" s="3"/>
@@ -5556,7 +5766,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="7">
-        <v>2026080941</v>
+        <v>2026080629</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -5565,46 +5775,48 @@
         <v>29</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>95</v>
+        <v>234</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>113</v>
+        <v>237</v>
       </c>
       <c r="K59" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L59" s="8" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="N59" s="8" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="O59" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P59" s="7"/>
       <c r="Q59" s="7">
-        <v>11287</v>
+        <v>3160</v>
       </c>
       <c r="R59" s="7">
-        <v>310496</v>
-      </c>
-      <c r="S59" s="7"/>
+        <v>415812</v>
+      </c>
+      <c r="S59" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T59" s="7"/>
       <c r="U59" s="7"/>
       <c r="V59" s="7"/>
@@ -5612,17 +5824,21 @@
       <c r="X59" s="7"/>
       <c r="Y59" s="7"/>
       <c r="Z59" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA59" s="7"/>
-      <c r="AB59" s="7"/>
+        <v>201</v>
+      </c>
+      <c r="AA59" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB59" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:28">
       <c r="A60" s="3">
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>2026080681</v>
+        <v>2026080630</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -5631,42 +5847,46 @@
         <v>29</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>42</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>43</v>
+        <v>234</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
+        <v>236</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L60" s="6" t="s">
-        <v>119</v>
+        <v>238</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P60" s="3"/>
-      <c r="Q60" s="3"/>
+      <c r="Q60" s="3">
+        <v>3160</v>
+      </c>
       <c r="R60" s="3">
-        <v>0</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>415812</v>
+      </c>
+      <c r="S60" s="3"/>
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
@@ -5674,21 +5894,19 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
       <c r="Z60" s="6" t="s">
-        <v>122</v>
+        <v>201</v>
       </c>
       <c r="AA60" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB60" s="3">
-        <v>1</v>
-      </c>
+      <c r="AB60" s="3"/>
     </row>
     <row r="61" spans="1:28">
       <c r="A61" s="7">
         <v>59</v>
       </c>
       <c r="B61" s="7">
-        <v>2026080993</v>
+        <v>2026080408</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -5697,30 +5915,34 @@
         <v>29</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>238</v>
+        <v>32</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
+        <v>241</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L61" s="8" t="s">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N61" s="8" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O61" s="7" t="s">
         <v>39</v>
@@ -5740,7 +5962,7 @@
       <c r="X61" s="7"/>
       <c r="Y61" s="7"/>
       <c r="Z61" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA61" s="7" t="s">
         <v>40</v>
@@ -5754,7 +5976,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="3">
-        <v>2026080656</v>
+        <v>2026081026</v>
       </c>
       <c r="C62" s="3">
         <v>1</v>
@@ -5763,42 +5985,46 @@
         <v>29</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>136</v>
+        <v>246</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
+        <v>248</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L62" s="6" t="s">
-        <v>119</v>
+        <v>249</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="O62" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P62" s="3"/>
-      <c r="Q62" s="3"/>
+      <c r="Q62" s="3">
+        <v>75</v>
+      </c>
       <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="S62" s="3"/>
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
@@ -5806,7 +6032,7 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
       <c r="Z62" s="6" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>40</v>
@@ -5820,7 +6046,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="7">
-        <v>2026080705</v>
+        <v>2026080440</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
@@ -5829,38 +6055,44 @@
         <v>29</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="J63" s="7"/>
-      <c r="K63" s="7"/>
+        <v>253</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L63" s="8" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="N63" s="8" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O63" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P63" s="7"/>
-      <c r="Q63" s="7"/>
+      <c r="Q63" s="7">
+        <v>7167</v>
+      </c>
       <c r="R63" s="7">
-        <v>0</v>
+        <v>39533</v>
       </c>
       <c r="S63" s="7" t="s">
         <v>40</v>
@@ -5872,21 +6104,17 @@
       <c r="X63" s="7"/>
       <c r="Y63" s="7"/>
       <c r="Z63" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA63" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB63" s="7">
-        <v>1</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="AA63" s="7"/>
+      <c r="AB63" s="7"/>
     </row>
     <row r="64" spans="1:28">
       <c r="A64" s="3">
         <v>62</v>
       </c>
       <c r="B64" s="3">
-        <v>2026080746</v>
+        <v>2026080441</v>
       </c>
       <c r="C64" s="3">
         <v>1</v>
@@ -5895,13 +6123,13 @@
         <v>29</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>252</v>
@@ -5909,10 +6137,14 @@
       <c r="I64" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
+      <c r="J64" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L64" s="6" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>254</v>
@@ -5921,16 +6153,16 @@
         <v>255</v>
       </c>
       <c r="O64" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P64" s="3"/>
-      <c r="Q64" s="3"/>
+      <c r="Q64" s="3">
+        <v>7167</v>
+      </c>
       <c r="R64" s="3">
-        <v>0</v>
-      </c>
-      <c r="S64" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>39533</v>
+      </c>
+      <c r="S64" s="3"/>
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
@@ -5938,21 +6170,17 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="AA64" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB64" s="3">
-        <v>1</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="AA64" s="3"/>
+      <c r="AB64" s="3"/>
     </row>
     <row r="65" spans="1:28">
       <c r="A65" s="7">
         <v>63</v>
       </c>
       <c r="B65" s="7">
-        <v>2026080561</v>
+        <v>2026080113</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -5961,28 +6189,28 @@
         <v>29</v>
       </c>
       <c r="E65" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I65" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="F65" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I65" s="7" t="s">
+      <c r="J65" s="7" t="s">
         <v>258</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>53</v>
       </c>
       <c r="K65" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L65" s="8" t="s">
-        <v>37</v>
+        <v>204</v>
       </c>
       <c r="M65" s="8" t="s">
         <v>259</v>
@@ -5993,14 +6221,10 @@
       <c r="O65" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="P65" s="7">
-        <v>2745</v>
-      </c>
-      <c r="Q65" s="7">
-        <v>3684</v>
-      </c>
+      <c r="P65" s="7"/>
+      <c r="Q65" s="7"/>
       <c r="R65" s="7">
-        <v>17102</v>
+        <v>251357</v>
       </c>
       <c r="S65" s="7"/>
       <c r="T65" s="7"/>
@@ -6010,21 +6234,17 @@
       <c r="X65" s="7"/>
       <c r="Y65" s="7"/>
       <c r="Z65" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA65" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB65" s="7">
-        <v>1</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="AA65" s="7"/>
+      <c r="AB65" s="7"/>
     </row>
     <row r="66" spans="1:28">
       <c r="A66" s="3">
         <v>64</v>
       </c>
       <c r="B66" s="3">
-        <v>2026080560</v>
+        <v>2026080112</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
@@ -6033,70 +6253,66 @@
         <v>29</v>
       </c>
       <c r="E66" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>262</v>
-      </c>
       <c r="J66" s="3" t="s">
-        <v>53</v>
+        <v>258</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>37</v>
+        <v>204</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="O66" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="P66" s="3">
-        <v>937</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>1866</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
       <c r="R66" s="3">
-        <v>12148</v>
-      </c>
-      <c r="S66" s="3"/>
+        <v>251357</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T66" s="3"/>
-      <c r="U66" s="3"/>
+      <c r="U66" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>1</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="AA66" s="3"/>
+      <c r="AB66" s="3"/>
     </row>
     <row r="67" spans="1:28">
       <c r="A67" s="7">
         <v>65</v>
       </c>
       <c r="B67" s="7">
-        <v>2026080159</v>
+        <v>2026080938</v>
       </c>
       <c r="C67" s="7">
         <v>1</v>
@@ -6105,46 +6321,48 @@
         <v>29</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>58</v>
+        <v>262</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="K67" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L67" s="8" t="s">
-        <v>61</v>
+        <v>264</v>
       </c>
       <c r="M67" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="N67" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="N67" s="8" t="s">
-        <v>267</v>
-      </c>
       <c r="O67" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P67" s="7"/>
       <c r="Q67" s="7">
-        <v>730</v>
+        <v>3815</v>
       </c>
       <c r="R67" s="7">
-        <v>5615</v>
-      </c>
-      <c r="S67" s="7"/>
+        <v>225709</v>
+      </c>
+      <c r="S67" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T67" s="7"/>
       <c r="U67" s="7"/>
       <c r="V67" s="7"/>
@@ -6152,21 +6370,17 @@
       <c r="X67" s="7"/>
       <c r="Y67" s="7"/>
       <c r="Z67" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA67" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB67" s="7">
-        <v>1</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="AA67" s="7"/>
+      <c r="AB67" s="7"/>
     </row>
     <row r="68" spans="1:28">
       <c r="A68" s="3">
         <v>66</v>
       </c>
       <c r="B68" s="3">
-        <v>2026080673</v>
+        <v>2026080939</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -6175,70 +6389,64 @@
         <v>29</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>61</v>
+        <v>264</v>
       </c>
       <c r="M68" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="N68" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="N68" s="6" t="s">
-        <v>267</v>
-      </c>
       <c r="O68" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P68" s="3"/>
       <c r="Q68" s="3">
-        <v>730</v>
+        <v>3815</v>
       </c>
       <c r="R68" s="3">
-        <v>5615</v>
+        <v>225709</v>
       </c>
       <c r="S68" s="3"/>
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
-      <c r="W68" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="W68" s="3"/>
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
       <c r="Z68" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="AA68" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB68" s="3">
-        <v>1</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="AA68" s="3"/>
+      <c r="AB68" s="3"/>
     </row>
     <row r="69" spans="1:28">
       <c r="A69" s="7">
         <v>67</v>
       </c>
       <c r="B69" s="7">
-        <v>2026080908</v>
+        <v>2026080940</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -6247,44 +6455,48 @@
         <v>29</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J69" s="7" t="s">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="K69" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L69" s="8" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="M69" s="8" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="N69" s="8" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="O69" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P69" s="7"/>
-      <c r="Q69" s="7"/>
+      <c r="Q69" s="7">
+        <v>11287</v>
+      </c>
       <c r="R69" s="7">
-        <v>3638</v>
-      </c>
-      <c r="S69" s="7"/>
+        <v>310496</v>
+      </c>
+      <c r="S69" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T69" s="7"/>
       <c r="U69" s="7"/>
       <c r="V69" s="7"/>
@@ -6292,21 +6504,17 @@
       <c r="X69" s="7"/>
       <c r="Y69" s="7"/>
       <c r="Z69" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA69" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB69" s="7">
-        <v>1</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="AA69" s="7"/>
+      <c r="AB69" s="7"/>
     </row>
     <row r="70" spans="1:28">
       <c r="A70" s="3">
         <v>68</v>
       </c>
       <c r="B70" s="3">
-        <v>2026080679</v>
+        <v>2026080941</v>
       </c>
       <c r="C70" s="3">
         <v>1</v>
@@ -6315,42 +6523,44 @@
         <v>29</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>43</v>
+        <v>267</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>64</v>
       </c>
       <c r="P70" s="3"/>
-      <c r="Q70" s="3"/>
+      <c r="Q70" s="3">
+        <v>11287</v>
+      </c>
       <c r="R70" s="3">
-        <v>59219</v>
+        <v>310496</v>
       </c>
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
@@ -6360,21 +6570,17 @@
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
       <c r="Z70" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA70" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>1</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="AA70" s="3"/>
+      <c r="AB70" s="3"/>
     </row>
     <row r="71" spans="1:28">
       <c r="A71" s="7">
         <v>69</v>
       </c>
       <c r="B71" s="7">
-        <v>2026080680</v>
+        <v>2026080681</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -6383,7 +6589,7 @@
         <v>29</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>42</v>
@@ -6392,35 +6598,33 @@
         <v>43</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>80</v>
+        <v>270</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="J71" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="K71" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
       <c r="L71" s="8" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="M71" s="8" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="N71" s="8" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="O71" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P71" s="7"/>
       <c r="Q71" s="7"/>
       <c r="R71" s="7">
-        <v>94136</v>
-      </c>
-      <c r="S71" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S71" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T71" s="7"/>
       <c r="U71" s="7"/>
       <c r="V71" s="7"/>
@@ -6428,7 +6632,7 @@
       <c r="X71" s="7"/>
       <c r="Y71" s="7"/>
       <c r="Z71" s="8" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="AA71" s="7" t="s">
         <v>40</v>
@@ -6442,7 +6646,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="3">
-        <v>2026080562</v>
+        <v>2026080993</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
@@ -6451,52 +6655,50 @@
         <v>29</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>32</v>
+        <v>274</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>226</v>
+        <v>275</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="J72" s="3"/>
+      <c r="K72" s="3"/>
       <c r="L72" s="6" t="s">
-        <v>283</v>
+        <v>140</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="O72" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P72" s="3"/>
       <c r="Q72" s="3"/>
       <c r="R72" s="3">
-        <v>203813</v>
+        <v>0</v>
       </c>
       <c r="S72" s="3"/>
-      <c r="T72" s="3"/>
+      <c r="T72" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
       <c r="W72" s="3"/>
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
       <c r="Z72" s="6" t="s">
-        <v>41</v>
+        <v>279</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>40</v>
@@ -6510,7 +6712,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7">
-        <v>2026080563</v>
+        <v>2026080656</v>
       </c>
       <c r="C73" s="7">
         <v>1</v>
@@ -6519,44 +6721,42 @@
         <v>29</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>226</v>
+        <v>163</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>98</v>
+        <v>280</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="J73" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K73" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="J73" s="7"/>
+      <c r="K73" s="7"/>
       <c r="L73" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M73" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="N73" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="M73" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="N73" s="8" t="s">
-        <v>288</v>
-      </c>
       <c r="O73" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P73" s="7"/>
       <c r="Q73" s="7"/>
       <c r="R73" s="7">
-        <v>219373</v>
-      </c>
-      <c r="S73" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S73" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T73" s="7"/>
       <c r="U73" s="7"/>
       <c r="V73" s="7"/>
@@ -6564,7 +6764,7 @@
       <c r="X73" s="7"/>
       <c r="Y73" s="7"/>
       <c r="Z73" s="8" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="AA73" s="7" t="s">
         <v>40</v>
@@ -6578,7 +6778,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="3">
-        <v>2026080459</v>
+        <v>2026081006</v>
       </c>
       <c r="C74" s="3">
         <v>1</v>
@@ -6587,34 +6787,34 @@
         <v>29</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>74</v>
+        <v>285</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>211</v>
+        <v>140</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="O74" s="3" t="s">
         <v>48</v>
@@ -6622,7 +6822,7 @@
       <c r="P74" s="3"/>
       <c r="Q74" s="3"/>
       <c r="R74" s="3">
-        <v>60429</v>
+        <v>0</v>
       </c>
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
@@ -6632,7 +6832,7 @@
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
       <c r="Z74" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AA74" s="3" t="s">
         <v>40</v>
@@ -6646,7 +6846,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="7">
-        <v>2026080911</v>
+        <v>2026081023</v>
       </c>
       <c r="C75" s="7">
         <v>1</v>
@@ -6655,42 +6855,42 @@
         <v>29</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="J75" s="7" t="s">
-        <v>83</v>
+        <v>290</v>
       </c>
       <c r="K75" s="7" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="L75" s="8" t="s">
-        <v>273</v>
+        <v>140</v>
       </c>
       <c r="M75" s="8" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="N75" s="8" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="O75" s="7" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="P75" s="7"/>
       <c r="Q75" s="7"/>
       <c r="R75" s="7">
-        <v>9386</v>
+        <v>0</v>
       </c>
       <c r="S75" s="7"/>
       <c r="T75" s="7"/>
@@ -6700,21 +6900,19 @@
       <c r="X75" s="7"/>
       <c r="Y75" s="7"/>
       <c r="Z75" s="8" t="s">
-        <v>41</v>
+        <v>291</v>
       </c>
       <c r="AA75" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB75" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB75" s="7"/>
     </row>
     <row r="76" spans="1:28">
       <c r="A76" s="3">
         <v>74</v>
       </c>
       <c r="B76" s="3">
-        <v>2026080747</v>
+        <v>2026080917</v>
       </c>
       <c r="C76" s="3">
         <v>1</v>
@@ -6723,42 +6921,42 @@
         <v>29</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G76" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="I76" s="3" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>83</v>
+        <v>147</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="O76" s="3" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="P76" s="3"/>
       <c r="Q76" s="3"/>
       <c r="R76" s="3">
-        <v>9338</v>
+        <v>0</v>
       </c>
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
@@ -6768,7 +6966,7 @@
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
       <c r="Z76" s="6" t="s">
-        <v>41</v>
+        <v>295</v>
       </c>
       <c r="AA76" s="3" t="s">
         <v>40</v>
@@ -6782,7 +6980,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="7">
-        <v>2026080914</v>
+        <v>2026081005</v>
       </c>
       <c r="C77" s="7">
         <v>1</v>
@@ -6791,44 +6989,42 @@
         <v>29</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>31</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>226</v>
+        <v>74</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="J77" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K77" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="J77" s="7"/>
+      <c r="K77" s="7"/>
       <c r="L77" s="8" t="s">
-        <v>273</v>
+        <v>140</v>
       </c>
       <c r="M77" s="8" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="N77" s="8" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="O77" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P77" s="7"/>
       <c r="Q77" s="7"/>
       <c r="R77" s="7">
-        <v>45877</v>
-      </c>
-      <c r="S77" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S77" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T77" s="7"/>
       <c r="U77" s="7"/>
       <c r="V77" s="7"/>
@@ -6836,21 +7032,19 @@
       <c r="X77" s="7"/>
       <c r="Y77" s="7"/>
       <c r="Z77" s="8" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="AA77" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB77" s="7">
-        <v>1</v>
-      </c>
+      <c r="AB77" s="7"/>
     </row>
     <row r="78" spans="1:28">
       <c r="A78" s="3">
         <v>76</v>
       </c>
       <c r="B78" s="3">
-        <v>2026080916</v>
+        <v>2026080705</v>
       </c>
       <c r="C78" s="3">
         <v>1</v>
@@ -6859,44 +7053,42 @@
         <v>29</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
       <c r="L78" s="6" t="s">
-        <v>273</v>
+        <v>140</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="O78" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P78" s="3"/>
       <c r="Q78" s="3"/>
       <c r="R78" s="3">
-        <v>57194</v>
-      </c>
-      <c r="S78" s="3"/>
+        <v>0</v>
+      </c>
+      <c r="S78" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T78" s="3"/>
       <c r="U78" s="3"/>
       <c r="V78" s="3"/>
@@ -6904,7 +7096,7 @@
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
       <c r="Z78" s="6" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="AA78" s="3" t="s">
         <v>40</v>
@@ -6918,7 +7110,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="7">
-        <v>2026080913</v>
+        <v>2026080746</v>
       </c>
       <c r="C79" s="7">
         <v>1</v>
@@ -6927,44 +7119,42 @@
         <v>29</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="K79" s="7" t="s">
-        <v>36</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="J79" s="7"/>
+      <c r="K79" s="7"/>
       <c r="L79" s="8" t="s">
-        <v>273</v>
+        <v>140</v>
       </c>
       <c r="M79" s="8" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="N79" s="8" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="O79" s="7" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P79" s="7"/>
       <c r="Q79" s="7"/>
       <c r="R79" s="7">
-        <v>36587</v>
-      </c>
-      <c r="S79" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="S79" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T79" s="7"/>
       <c r="U79" s="7"/>
       <c r="V79" s="7"/>
@@ -6972,7 +7162,7 @@
       <c r="X79" s="7"/>
       <c r="Y79" s="7"/>
       <c r="Z79" s="8" t="s">
-        <v>41</v>
+        <v>304</v>
       </c>
       <c r="AA79" s="7" t="s">
         <v>40</v>
@@ -6986,7 +7176,7 @@
         <v>78</v>
       </c>
       <c r="B80" s="3">
-        <v>2026080910</v>
+        <v>2026081051</v>
       </c>
       <c r="C80" s="3">
         <v>1</v>
@@ -6995,42 +7185,42 @@
         <v>29</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>165</v>
+        <v>307</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="K80" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>312</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="N80" s="6"/>
       <c r="O80" s="3" t="s">
         <v>64</v>
       </c>
       <c r="P80" s="3"/>
-      <c r="Q80" s="3"/>
+      <c r="Q80" s="3">
+        <v>2650</v>
+      </c>
       <c r="R80" s="3">
-        <v>41847</v>
+        <v>53000</v>
       </c>
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
@@ -7054,7 +7244,7 @@
         <v>79</v>
       </c>
       <c r="B81" s="7">
-        <v>2026080909</v>
+        <v>2026080561</v>
       </c>
       <c r="C81" s="7">
         <v>1</v>
@@ -7063,42 +7253,46 @@
         <v>29</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>271</v>
+        <v>197</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>309</v>
+        <v>32</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="K81" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L81" s="8" t="s">
-        <v>273</v>
+        <v>37</v>
       </c>
       <c r="M81" s="8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="N81" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O81" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="P81" s="7"/>
-      <c r="Q81" s="7"/>
+      <c r="P81" s="7">
+        <v>2745</v>
+      </c>
+      <c r="Q81" s="7">
+        <v>3684</v>
+      </c>
       <c r="R81" s="7">
-        <v>22007</v>
+        <v>17102</v>
       </c>
       <c r="S81" s="7"/>
       <c r="T81" s="7"/>
@@ -7122,7 +7316,7 @@
         <v>80</v>
       </c>
       <c r="B82" s="3">
-        <v>2026080425</v>
+        <v>2026080560</v>
       </c>
       <c r="C82" s="3">
         <v>1</v>
@@ -7131,44 +7325,46 @@
         <v>29</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>136</v>
+        <v>307</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>317</v>
+        <v>53</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>211</v>
+        <v>37</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O82" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="P82" s="3"/>
+      <c r="P82" s="3">
+        <v>937</v>
+      </c>
       <c r="Q82" s="3">
-        <v>2</v>
+        <v>1866</v>
       </c>
       <c r="R82" s="3">
-        <v>6</v>
+        <v>12148</v>
       </c>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
@@ -7192,7 +7388,7 @@
         <v>81</v>
       </c>
       <c r="B83" s="7">
-        <v>2026080092</v>
+        <v>2026080159</v>
       </c>
       <c r="C83" s="7">
         <v>1</v>
@@ -7201,42 +7397,44 @@
         <v>29</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>136</v>
+        <v>58</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>321</v>
+        <v>53</v>
       </c>
       <c r="K83" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L83" s="8" t="s">
-        <v>322</v>
+        <v>61</v>
       </c>
       <c r="M83" s="8" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="N83" s="8" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="O83" s="7" t="s">
         <v>64</v>
       </c>
       <c r="P83" s="7"/>
-      <c r="Q83" s="7"/>
+      <c r="Q83" s="7">
+        <v>730</v>
+      </c>
       <c r="R83" s="7">
-        <v>123517</v>
+        <v>5615</v>
       </c>
       <c r="S83" s="7"/>
       <c r="T83" s="7"/>
@@ -7260,7 +7458,7 @@
         <v>82</v>
       </c>
       <c r="B84" s="3">
-        <v>2026080912</v>
+        <v>2026080673</v>
       </c>
       <c r="C84" s="3">
         <v>1</v>
@@ -7269,52 +7467,56 @@
         <v>29</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>321</v>
+        <v>53</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>273</v>
+        <v>61</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="O84" s="3" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="P84" s="3"/>
-      <c r="Q84" s="3"/>
+      <c r="Q84" s="3">
+        <v>730</v>
+      </c>
       <c r="R84" s="3">
-        <v>1042</v>
+        <v>5615</v>
       </c>
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
-      <c r="W84" s="3"/>
+      <c r="W84" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="X84" s="3"/>
       <c r="Y84" s="3"/>
       <c r="Z84" s="6" t="s">
-        <v>41</v>
+        <v>321</v>
       </c>
       <c r="AA84" s="3" t="s">
         <v>40</v>
@@ -7328,7 +7530,7 @@
         <v>83</v>
       </c>
       <c r="B85" s="7">
-        <v>2026080915</v>
+        <v>2026081064</v>
       </c>
       <c r="C85" s="7">
         <v>1</v>
@@ -7337,42 +7539,44 @@
         <v>29</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>106</v>
+        <v>307</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>321</v>
+        <v>53</v>
       </c>
       <c r="K85" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L85" s="8" t="s">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="M85" s="8" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="N85" s="8" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="O85" s="7" t="s">
         <v>64</v>
       </c>
       <c r="P85" s="7"/>
-      <c r="Q85" s="7"/>
+      <c r="Q85" s="7">
+        <v>12181</v>
+      </c>
       <c r="R85" s="7">
-        <v>6537</v>
+        <v>9668</v>
       </c>
       <c r="S85" s="7"/>
       <c r="T85" s="7"/>
@@ -7396,7 +7600,7 @@
         <v>84</v>
       </c>
       <c r="B86" s="3">
-        <v>2026080674</v>
+        <v>2026081067</v>
       </c>
       <c r="C86" s="3">
         <v>1</v>
@@ -7405,44 +7609,44 @@
         <v>29</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>136</v>
+        <v>262</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="O86" s="3" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="P86" s="3"/>
       <c r="Q86" s="3">
-        <v>49837</v>
+        <v>12181</v>
       </c>
       <c r="R86" s="3">
-        <v>80692</v>
+        <v>9668</v>
       </c>
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
@@ -7452,7 +7656,7 @@
       <c r="X86" s="3"/>
       <c r="Y86" s="3"/>
       <c r="Z86" s="6" t="s">
-        <v>41</v>
+        <v>326</v>
       </c>
       <c r="AA86" s="3" t="s">
         <v>40</v>
@@ -7466,7 +7670,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="7">
-        <v>2026080256</v>
+        <v>2026080908</v>
       </c>
       <c r="C87" s="7">
         <v>1</v>
@@ -7475,34 +7679,34 @@
         <v>29</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>106</v>
+        <v>306</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>95</v>
+        <v>327</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>335</v>
+        <v>77</v>
       </c>
       <c r="K87" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L87" s="8" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="M87" s="8" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="N87" s="8" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="O87" s="7" t="s">
         <v>64</v>
@@ -7510,7 +7714,7 @@
       <c r="P87" s="7"/>
       <c r="Q87" s="7"/>
       <c r="R87" s="7">
-        <v>47549</v>
+        <v>3638</v>
       </c>
       <c r="S87" s="7"/>
       <c r="T87" s="7"/>
@@ -7534,7 +7738,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="3">
-        <v>2026080063</v>
+        <v>2026080679</v>
       </c>
       <c r="C88" s="3">
         <v>1</v>
@@ -7543,34 +7747,34 @@
         <v>29</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>32</v>
+        <v>202</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>226</v>
+        <v>43</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>335</v>
+        <v>77</v>
       </c>
       <c r="K88" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>322</v>
+        <v>84</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="O88" s="3" t="s">
         <v>64</v>
@@ -7578,7 +7782,7 @@
       <c r="P88" s="3"/>
       <c r="Q88" s="3"/>
       <c r="R88" s="3">
-        <v>23606</v>
+        <v>59219</v>
       </c>
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
@@ -7602,7 +7806,7 @@
         <v>87</v>
       </c>
       <c r="B89" s="7">
-        <v>2026080064</v>
+        <v>2026080680</v>
       </c>
       <c r="C89" s="7">
         <v>1</v>
@@ -7611,66 +7815,66 @@
         <v>29</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>226</v>
+        <v>43</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>342</v>
+        <v>88</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="J89" s="7" t="s">
-        <v>335</v>
+        <v>77</v>
       </c>
       <c r="K89" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>322</v>
+        <v>84</v>
       </c>
       <c r="M89" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="N89" s="8" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="O89" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P89" s="7"/>
       <c r="Q89" s="7"/>
       <c r="R89" s="7">
-        <v>23606</v>
+        <v>94136</v>
       </c>
       <c r="S89" s="7"/>
       <c r="T89" s="7"/>
-      <c r="U89" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U89" s="7"/>
       <c r="V89" s="7"/>
       <c r="W89" s="7"/>
       <c r="X89" s="7"/>
       <c r="Y89" s="7"/>
       <c r="Z89" s="8" t="s">
-        <v>343</v>
+        <v>41</v>
       </c>
       <c r="AA89" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB89" s="7"/>
+      <c r="AB89" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:28">
       <c r="A90" s="3">
         <v>88</v>
       </c>
       <c r="B90" s="3">
-        <v>2026080060</v>
+        <v>2026080562</v>
       </c>
       <c r="C90" s="3">
         <v>1</v>
@@ -7679,34 +7883,34 @@
         <v>29</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>261</v>
+        <v>32</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>165</v>
+        <v>262</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>335</v>
+        <v>91</v>
       </c>
       <c r="K90" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="O90" s="3" t="s">
         <v>64</v>
@@ -7714,7 +7918,7 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3">
-        <v>118283</v>
+        <v>203813</v>
       </c>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
@@ -7738,7 +7942,7 @@
         <v>89</v>
       </c>
       <c r="B91" s="7">
-        <v>2026080066</v>
+        <v>2026080563</v>
       </c>
       <c r="C91" s="7">
         <v>1</v>
@@ -7747,54 +7951,52 @@
         <v>29</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>98</v>
+        <v>262</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>335</v>
+        <v>91</v>
       </c>
       <c r="K91" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L91" s="8" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="M91" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="N91" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O91" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P91" s="7"/>
       <c r="Q91" s="7"/>
       <c r="R91" s="7">
-        <v>118283</v>
+        <v>219373</v>
       </c>
       <c r="S91" s="7"/>
       <c r="T91" s="7"/>
-      <c r="U91" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U91" s="7"/>
       <c r="V91" s="7"/>
       <c r="W91" s="7"/>
       <c r="X91" s="7"/>
       <c r="Y91" s="7"/>
       <c r="Z91" s="8" t="s">
-        <v>343</v>
+        <v>41</v>
       </c>
       <c r="AA91" s="7" t="s">
         <v>40</v>
@@ -7808,7 +8010,7 @@
         <v>90</v>
       </c>
       <c r="B92" s="3">
-        <v>2026080111</v>
+        <v>2026080459</v>
       </c>
       <c r="C92" s="3">
         <v>1</v>
@@ -7817,42 +8019,42 @@
         <v>29</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>170</v>
+        <v>296</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>335</v>
+        <v>91</v>
       </c>
       <c r="K92" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>322</v>
+        <v>242</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="O92" s="3" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="P92" s="3"/>
       <c r="Q92" s="3"/>
       <c r="R92" s="3">
-        <v>260202</v>
+        <v>60429</v>
       </c>
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
@@ -7862,7 +8064,7 @@
       <c r="X92" s="3"/>
       <c r="Y92" s="3"/>
       <c r="Z92" s="6" t="s">
-        <v>41</v>
+        <v>326</v>
       </c>
       <c r="AA92" s="3" t="s">
         <v>40</v>
@@ -7876,7 +8078,7 @@
         <v>91</v>
       </c>
       <c r="B93" s="7">
-        <v>2026080131</v>
+        <v>2026080911</v>
       </c>
       <c r="C93" s="7">
         <v>1</v>
@@ -7885,66 +8087,66 @@
         <v>29</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>335</v>
+        <v>91</v>
       </c>
       <c r="K93" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L93" s="8" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M93" s="8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N93" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="O93" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P93" s="7"/>
       <c r="Q93" s="7"/>
       <c r="R93" s="7">
-        <v>260202</v>
+        <v>9386</v>
       </c>
       <c r="S93" s="7"/>
       <c r="T93" s="7"/>
-      <c r="U93" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U93" s="7"/>
       <c r="V93" s="7"/>
       <c r="W93" s="7"/>
       <c r="X93" s="7"/>
       <c r="Y93" s="7"/>
       <c r="Z93" s="8" t="s">
-        <v>343</v>
+        <v>41</v>
       </c>
       <c r="AA93" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="AB93" s="7"/>
+      <c r="AB93" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:28">
       <c r="A94" s="3">
         <v>92</v>
       </c>
       <c r="B94" s="3">
-        <v>2026080132</v>
+        <v>2026080747</v>
       </c>
       <c r="C94" s="3">
         <v>1</v>
@@ -7953,42 +8155,42 @@
         <v>29</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>350</v>
+        <v>74</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>335</v>
+        <v>91</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>322</v>
+        <v>84</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>349</v>
+        <v>319</v>
       </c>
       <c r="O94" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P94" s="3"/>
       <c r="Q94" s="3"/>
       <c r="R94" s="3">
-        <v>260202</v>
+        <v>9338</v>
       </c>
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
@@ -7998,19 +8200,21 @@
       <c r="X94" s="3"/>
       <c r="Y94" s="3"/>
       <c r="Z94" s="6" t="s">
-        <v>352</v>
+        <v>41</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB94" s="3"/>
+      <c r="AB94" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:28">
       <c r="A95" s="7">
         <v>93</v>
       </c>
       <c r="B95" s="7">
-        <v>2026080061</v>
+        <v>2026080914</v>
       </c>
       <c r="C95" s="7">
         <v>1</v>
@@ -8019,34 +8223,34 @@
         <v>29</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>165</v>
+        <v>262</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J95" s="7" t="s">
-        <v>335</v>
+        <v>91</v>
       </c>
       <c r="K95" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L95" s="8" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M95" s="8" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N95" s="8" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O95" s="7" t="s">
         <v>64</v>
@@ -8054,7 +8258,7 @@
       <c r="P95" s="7"/>
       <c r="Q95" s="7"/>
       <c r="R95" s="7">
-        <v>191131</v>
+        <v>45877</v>
       </c>
       <c r="S95" s="7"/>
       <c r="T95" s="7"/>
@@ -8078,7 +8282,7 @@
         <v>94</v>
       </c>
       <c r="B96" s="3">
-        <v>2026080065</v>
+        <v>2026080916</v>
       </c>
       <c r="C96" s="3">
         <v>1</v>
@@ -8087,54 +8291,52 @@
         <v>29</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>342</v>
+        <v>81</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>98</v>
+        <v>320</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>335</v>
+        <v>91</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="O96" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P96" s="3"/>
       <c r="Q96" s="3"/>
       <c r="R96" s="3">
-        <v>191131</v>
+        <v>57194</v>
       </c>
       <c r="S96" s="3"/>
       <c r="T96" s="3"/>
-      <c r="U96" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="U96" s="3"/>
       <c r="V96" s="3"/>
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
       <c r="Y96" s="3"/>
       <c r="Z96" s="6" t="s">
-        <v>343</v>
+        <v>41</v>
       </c>
       <c r="AA96" s="3" t="s">
         <v>40</v>
@@ -8148,7 +8350,7 @@
         <v>95</v>
       </c>
       <c r="B97" s="7">
-        <v>2026080458</v>
+        <v>2026080913</v>
       </c>
       <c r="C97" s="7">
         <v>1</v>
@@ -8157,42 +8359,42 @@
         <v>29</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="J97" s="7" t="s">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="K97" s="7" t="s">
         <v>36</v>
       </c>
       <c r="L97" s="8" t="s">
-        <v>211</v>
+        <v>329</v>
       </c>
       <c r="M97" s="8" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="N97" s="8" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="O97" s="7" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P97" s="7"/>
       <c r="Q97" s="7"/>
       <c r="R97" s="7">
-        <v>47584</v>
+        <v>36587</v>
       </c>
       <c r="S97" s="7"/>
       <c r="T97" s="7"/>
@@ -8202,7 +8404,7 @@
       <c r="X97" s="7"/>
       <c r="Y97" s="7"/>
       <c r="Z97" s="8" t="s">
-        <v>292</v>
+        <v>41</v>
       </c>
       <c r="AA97" s="7" t="s">
         <v>40</v>
@@ -8216,7 +8418,7 @@
         <v>96</v>
       </c>
       <c r="B98" s="3">
-        <v>2026080457</v>
+        <v>2026080910</v>
       </c>
       <c r="C98" s="3">
         <v>1</v>
@@ -8225,42 +8427,42 @@
         <v>29</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>170</v>
+        <v>364</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>43</v>
+        <v>197</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="K98" s="3" t="s">
         <v>36</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>211</v>
+        <v>329</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="O98" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P98" s="3"/>
       <c r="Q98" s="3"/>
       <c r="R98" s="3">
-        <v>505328</v>
+        <v>41847</v>
       </c>
       <c r="S98" s="3"/>
       <c r="T98" s="3"/>
@@ -8270,7 +8472,7 @@
       <c r="X98" s="3"/>
       <c r="Y98" s="3"/>
       <c r="Z98" s="6" t="s">
-        <v>361</v>
+        <v>41</v>
       </c>
       <c r="AA98" s="3" t="s">
         <v>40</v>
@@ -8284,7 +8486,7 @@
         <v>97</v>
       </c>
       <c r="B99" s="7">
-        <v>2026080539</v>
+        <v>2026080909</v>
       </c>
       <c r="C99" s="7">
         <v>1</v>
@@ -8293,42 +8495,42 @@
         <v>29</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>248</v>
+        <v>327</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>58</v>
+        <v>364</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="K99" s="7" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="L99" s="8" t="s">
-        <v>119</v>
+        <v>329</v>
       </c>
       <c r="M99" s="8" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="N99" s="8" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="O99" s="7" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P99" s="7"/>
       <c r="Q99" s="7"/>
       <c r="R99" s="7">
-        <v>0</v>
+        <v>22007</v>
       </c>
       <c r="S99" s="7"/>
       <c r="T99" s="7"/>
@@ -8338,7 +8540,7 @@
       <c r="X99" s="7"/>
       <c r="Y99" s="7"/>
       <c r="Z99" s="8" t="s">
-        <v>365</v>
+        <v>41</v>
       </c>
       <c r="AA99" s="7" t="s">
         <v>40</v>
@@ -8352,7 +8554,7 @@
         <v>98</v>
       </c>
       <c r="B100" s="3">
-        <v>2026080991</v>
+        <v>2026080425</v>
       </c>
       <c r="C100" s="3">
         <v>1</v>
@@ -8361,50 +8563,54 @@
         <v>29</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>238</v>
+        <v>163</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>366</v>
+        <v>202</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J100" s="3"/>
-      <c r="K100" s="3"/>
+        <v>371</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L100" s="6" t="s">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>241</v>
+        <v>373</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>242</v>
+        <v>374</v>
       </c>
       <c r="O100" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P100" s="3"/>
-      <c r="Q100" s="3"/>
+      <c r="Q100" s="3">
+        <v>2</v>
+      </c>
       <c r="R100" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S100" s="3"/>
-      <c r="T100" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="T100" s="3"/>
       <c r="U100" s="3"/>
       <c r="V100" s="3"/>
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
       <c r="Y100" s="3"/>
       <c r="Z100" s="6" t="s">
-        <v>367</v>
+        <v>41</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>40</v>
@@ -8418,7 +8624,7 @@
         <v>99</v>
       </c>
       <c r="B101" s="7">
-        <v>2026080058</v>
+        <v>2026080092</v>
       </c>
       <c r="C101" s="7">
         <v>1</v>
@@ -8427,42 +8633,42 @@
         <v>29</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="J101" s="7" t="s">
-        <v>126</v>
+        <v>376</v>
       </c>
       <c r="K101" s="7" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="L101" s="8" t="s">
-        <v>119</v>
+        <v>377</v>
       </c>
       <c r="M101" s="8" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="N101" s="8" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="O101" s="7" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P101" s="7"/>
       <c r="Q101" s="7"/>
       <c r="R101" s="7">
-        <v>0</v>
+        <v>123517</v>
       </c>
       <c r="S101" s="7"/>
       <c r="T101" s="7"/>
@@ -8472,7 +8678,7 @@
       <c r="X101" s="7"/>
       <c r="Y101" s="7"/>
       <c r="Z101" s="8" t="s">
-        <v>371</v>
+        <v>41</v>
       </c>
       <c r="AA101" s="7" t="s">
         <v>40</v>
@@ -8486,7 +8692,7 @@
         <v>100</v>
       </c>
       <c r="B102" s="3">
-        <v>2026080239</v>
+        <v>2026081066</v>
       </c>
       <c r="C102" s="3">
         <v>1</v>
@@ -8495,64 +8701,66 @@
         <v>29</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>226</v>
+        <v>32</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>106</v>
+        <v>262</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="J102" s="3"/>
-      <c r="K102" s="3"/>
+        <v>380</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="L102" s="6" t="s">
-        <v>119</v>
+        <v>323</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="O102" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P102" s="3"/>
       <c r="Q102" s="3"/>
       <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>40</v>
-      </c>
+        <v>16051</v>
+      </c>
+      <c r="S102" s="3"/>
       <c r="T102" s="3"/>
       <c r="U102" s="3"/>
       <c r="V102" s="3"/>
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
-      <c r="Y102" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y102" s="3"/>
       <c r="Z102" s="6" t="s">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AB102" s="3"/>
+      <c r="AB102" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="103" spans="1:28">
       <c r="A103" s="7">
         <v>101</v>
       </c>
       <c r="B103" s="7">
-        <v>2026080059</v>
+        <v>2026080912</v>
       </c>
       <c r="C103" s="7">
         <v>1</v>
@@ -8561,42 +8769,42 @@
         <v>29</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>165</v>
+        <v>348</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="J103" s="7" t="s">
-        <v>126</v>
+        <v>376</v>
       </c>
       <c r="K103" s="7" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="L103" s="8" t="s">
-        <v>119</v>
+        <v>329</v>
       </c>
       <c r="M103" s="8" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="N103" s="8" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="O103" s="7" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P103" s="7"/>
       <c r="Q103" s="7"/>
       <c r="R103" s="7">
-        <v>0</v>
+        <v>1042</v>
       </c>
       <c r="S103" s="7"/>
       <c r="T103" s="7"/>
@@ -8606,7 +8814,7 @@
       <c r="X103" s="7"/>
       <c r="Y103" s="7"/>
       <c r="Z103" s="8" t="s">
-        <v>371</v>
+        <v>41</v>
       </c>
       <c r="AA103" s="7" t="s">
         <v>40</v>
@@ -8620,7 +8828,7 @@
         <v>102</v>
       </c>
       <c r="B104" s="3">
-        <v>2026080400</v>
+        <v>2026080915</v>
       </c>
       <c r="C104" s="3">
         <v>1</v>
@@ -8629,42 +8837,42 @@
         <v>29</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>375</v>
+        <v>81</v>
       </c>
       <c r="I104" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="J104" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="J104" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="K104" s="3" t="s">
-        <v>127</v>
+        <v>36</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>119</v>
+        <v>329</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="O104" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="P104" s="3"/>
       <c r="Q104" s="3"/>
       <c r="R104" s="3">
-        <v>0</v>
+        <v>6537</v>
       </c>
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
@@ -8674,7 +8882,7 @@
       <c r="X104" s="3"/>
       <c r="Y104" s="3"/>
       <c r="Z104" s="6" t="s">
-        <v>379</v>
+        <v>41</v>
       </c>
       <c r="AA104" s="3" t="s">
         <v>40</v>
@@ -8688,7 +8896,7 @@
         <v>103</v>
       </c>
       <c r="B105" s="7">
-        <v>2026080406</v>
+        <v>2026081087</v>
       </c>
       <c r="C105" s="7">
         <v>1</v>
@@ -8697,90 +8905,1716 @@
         <v>29</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>375</v>
+        <v>163</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="I105" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="J105" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="J105" s="7"/>
-      <c r="K105" s="7"/>
+      <c r="K105" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="L105" s="8" t="s">
-        <v>119</v>
+        <v>390</v>
       </c>
       <c r="M105" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="N105" s="8" t="s">
-        <v>378</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="N105" s="8"/>
       <c r="O105" s="7" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="P105" s="7"/>
       <c r="Q105" s="7"/>
       <c r="R105" s="7">
-        <v>0</v>
-      </c>
-      <c r="S105" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>175481</v>
+      </c>
+      <c r="S105" s="7"/>
       <c r="T105" s="7"/>
       <c r="U105" s="7"/>
       <c r="V105" s="7"/>
       <c r="W105" s="7"/>
       <c r="X105" s="7"/>
-      <c r="Y105" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="Y105" s="7"/>
       <c r="Z105" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA105" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB105" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28">
+      <c r="A106" s="3">
+        <v>104</v>
+      </c>
+      <c r="B106" s="3">
+        <v>2026080674</v>
+      </c>
+      <c r="C106" s="3">
+        <v>1</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="J106" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K106" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L106" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="M106" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="N106" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="O106" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="P106" s="3"/>
+      <c r="Q106" s="3">
+        <v>49837</v>
+      </c>
+      <c r="R106" s="3">
+        <v>80692</v>
+      </c>
+      <c r="S106" s="3"/>
+      <c r="T106" s="3"/>
+      <c r="U106" s="3"/>
+      <c r="V106" s="3"/>
+      <c r="W106" s="3"/>
+      <c r="X106" s="3"/>
+      <c r="Y106" s="3"/>
+      <c r="Z106" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA106" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB106" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28">
+      <c r="A107" s="7">
+        <v>105</v>
+      </c>
+      <c r="B107" s="7">
+        <v>2026080256</v>
+      </c>
+      <c r="C107" s="7">
+        <v>1</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H107" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="I107" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="J107" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="K107" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L107" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="M107" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="N107" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="O107" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="P107" s="7"/>
+      <c r="Q107" s="7"/>
+      <c r="R107" s="7">
+        <v>47549</v>
+      </c>
+      <c r="S107" s="7"/>
+      <c r="T107" s="7"/>
+      <c r="U107" s="7"/>
+      <c r="V107" s="7"/>
+      <c r="W107" s="7"/>
+      <c r="X107" s="7"/>
+      <c r="Y107" s="7"/>
+      <c r="Z107" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA107" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB107" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28">
+      <c r="A108" s="3">
+        <v>106</v>
+      </c>
+      <c r="B108" s="3">
+        <v>2026080063</v>
+      </c>
+      <c r="C108" s="3">
+        <v>1</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="J108" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K108" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L108" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="O108" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="P108" s="3"/>
+      <c r="Q108" s="3"/>
+      <c r="R108" s="3">
+        <v>23606</v>
+      </c>
+      <c r="S108" s="3"/>
+      <c r="T108" s="3"/>
+      <c r="U108" s="3"/>
+      <c r="V108" s="3"/>
+      <c r="W108" s="3"/>
+      <c r="X108" s="3"/>
+      <c r="Y108" s="3"/>
+      <c r="Z108" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA108" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB108" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28">
+      <c r="A109" s="7">
+        <v>107</v>
+      </c>
+      <c r="B109" s="7">
+        <v>2026080064</v>
+      </c>
+      <c r="C109" s="7">
+        <v>1</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G109" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="I109" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="J109" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="K109" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="M109" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="N109" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="O109" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P109" s="7"/>
+      <c r="Q109" s="7"/>
+      <c r="R109" s="7">
+        <v>23606</v>
+      </c>
+      <c r="S109" s="7"/>
+      <c r="T109" s="7"/>
+      <c r="U109" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V109" s="7"/>
+      <c r="W109" s="7"/>
+      <c r="X109" s="7"/>
+      <c r="Y109" s="7"/>
+      <c r="Z109" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="AA109" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB109" s="7"/>
+    </row>
+    <row r="110" spans="1:28">
+      <c r="A110" s="3">
+        <v>108</v>
+      </c>
+      <c r="B110" s="3">
+        <v>2026080060</v>
+      </c>
+      <c r="C110" s="3">
+        <v>1</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="J110" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K110" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L110" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="N110" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="O110" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="P110" s="3"/>
+      <c r="Q110" s="3"/>
+      <c r="R110" s="3">
+        <v>118283</v>
+      </c>
+      <c r="S110" s="3"/>
+      <c r="T110" s="3"/>
+      <c r="U110" s="3"/>
+      <c r="V110" s="3"/>
+      <c r="W110" s="3"/>
+      <c r="X110" s="3"/>
+      <c r="Y110" s="3"/>
+      <c r="Z110" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA110" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB110" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28">
+      <c r="A111" s="7">
+        <v>109</v>
+      </c>
+      <c r="B111" s="7">
+        <v>2026080066</v>
+      </c>
+      <c r="C111" s="7">
+        <v>1</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H111" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="I111" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="J111" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="K111" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L111" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="M111" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="N111" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="O111" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P111" s="7"/>
+      <c r="Q111" s="7"/>
+      <c r="R111" s="7">
+        <v>118283</v>
+      </c>
+      <c r="S111" s="7"/>
+      <c r="T111" s="7"/>
+      <c r="U111" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V111" s="7"/>
+      <c r="W111" s="7"/>
+      <c r="X111" s="7"/>
+      <c r="Y111" s="7"/>
+      <c r="Z111" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="AA111" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB111" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:28">
+      <c r="A112" s="3">
+        <v>110</v>
+      </c>
+      <c r="B112" s="3">
+        <v>2026080111</v>
+      </c>
+      <c r="C112" s="3">
+        <v>1</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="J112" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K112" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L112" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="M112" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="N112" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="O112" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="P112" s="3"/>
+      <c r="Q112" s="3"/>
+      <c r="R112" s="3">
+        <v>260202</v>
+      </c>
+      <c r="S112" s="3"/>
+      <c r="T112" s="3"/>
+      <c r="U112" s="3"/>
+      <c r="V112" s="3"/>
+      <c r="W112" s="3"/>
+      <c r="X112" s="3"/>
+      <c r="Y112" s="3"/>
+      <c r="Z112" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA112" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB112" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28">
+      <c r="A113" s="7">
+        <v>111</v>
+      </c>
+      <c r="B113" s="7">
+        <v>2026080131</v>
+      </c>
+      <c r="C113" s="7">
+        <v>1</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="I113" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="J113" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="K113" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="M113" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="N113" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="O113" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P113" s="7"/>
+      <c r="Q113" s="7"/>
+      <c r="R113" s="7">
+        <v>260202</v>
+      </c>
+      <c r="S113" s="7"/>
+      <c r="T113" s="7"/>
+      <c r="U113" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="V113" s="7"/>
+      <c r="W113" s="7"/>
+      <c r="X113" s="7"/>
+      <c r="Y113" s="7"/>
+      <c r="Z113" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="AA113" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB113" s="7"/>
+    </row>
+    <row r="114" spans="1:28">
+      <c r="A114" s="3">
+        <v>112</v>
+      </c>
+      <c r="B114" s="3">
+        <v>2026080132</v>
+      </c>
+      <c r="C114" s="3">
+        <v>1</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K114" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L114" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="M114" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="N114" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="O114" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P114" s="3"/>
+      <c r="Q114" s="3"/>
+      <c r="R114" s="3">
+        <v>260202</v>
+      </c>
+      <c r="S114" s="3"/>
+      <c r="T114" s="3"/>
+      <c r="U114" s="3"/>
+      <c r="V114" s="3"/>
+      <c r="W114" s="3"/>
+      <c r="X114" s="3"/>
+      <c r="Y114" s="3"/>
+      <c r="Z114" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="AA114" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB114" s="3"/>
+    </row>
+    <row r="115" spans="1:28">
+      <c r="A115" s="7">
+        <v>113</v>
+      </c>
+      <c r="B115" s="7">
+        <v>2026080061</v>
+      </c>
+      <c r="C115" s="7">
+        <v>1</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="J115" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="K115" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L115" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="M115" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="N115" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="O115" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="P115" s="7"/>
+      <c r="Q115" s="7"/>
+      <c r="R115" s="7">
+        <v>191131</v>
+      </c>
+      <c r="S115" s="7"/>
+      <c r="T115" s="7"/>
+      <c r="U115" s="7"/>
+      <c r="V115" s="7"/>
+      <c r="W115" s="7"/>
+      <c r="X115" s="7"/>
+      <c r="Y115" s="7"/>
+      <c r="Z115" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA115" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB115" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28">
+      <c r="A116" s="3">
+        <v>114</v>
+      </c>
+      <c r="B116" s="3">
+        <v>2026080065</v>
+      </c>
+      <c r="C116" s="3">
+        <v>1</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K116" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L116" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="M116" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="N116" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="O116" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P116" s="3"/>
+      <c r="Q116" s="3"/>
+      <c r="R116" s="3">
+        <v>191131</v>
+      </c>
+      <c r="S116" s="3"/>
+      <c r="T116" s="3"/>
+      <c r="U116" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V116" s="3"/>
+      <c r="W116" s="3"/>
+      <c r="X116" s="3"/>
+      <c r="Y116" s="3"/>
+      <c r="Z116" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="AA116" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB116" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28">
+      <c r="A117" s="7">
+        <v>115</v>
+      </c>
+      <c r="B117" s="7">
+        <v>2026081076</v>
+      </c>
+      <c r="C117" s="7">
+        <v>1</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="J117" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="K117" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L117" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="M117" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="N117" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="O117" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="P117" s="7"/>
+      <c r="Q117" s="7"/>
+      <c r="R117" s="7">
+        <v>7629</v>
+      </c>
+      <c r="S117" s="7"/>
+      <c r="T117" s="7"/>
+      <c r="U117" s="7"/>
+      <c r="V117" s="7"/>
+      <c r="W117" s="7"/>
+      <c r="X117" s="7"/>
+      <c r="Y117" s="7"/>
+      <c r="Z117" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA117" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB117" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28">
+      <c r="A118" s="3">
+        <v>116</v>
+      </c>
+      <c r="B118" s="3">
+        <v>2026081065</v>
+      </c>
+      <c r="C118" s="3">
+        <v>1</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="K118" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L118" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="M118" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="N118" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="O118" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="P118" s="3"/>
+      <c r="Q118" s="3"/>
+      <c r="R118" s="3">
+        <v>584</v>
+      </c>
+      <c r="S118" s="3"/>
+      <c r="T118" s="3"/>
+      <c r="U118" s="3"/>
+      <c r="V118" s="3"/>
+      <c r="W118" s="3"/>
+      <c r="X118" s="3"/>
+      <c r="Y118" s="3"/>
+      <c r="Z118" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA118" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB118" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28">
+      <c r="A119" s="7">
+        <v>117</v>
+      </c>
+      <c r="B119" s="7">
+        <v>2026080458</v>
+      </c>
+      <c r="C119" s="7">
+        <v>1</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I119" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="J119" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="K119" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L119" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M119" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="N119" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="O119" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P119" s="7"/>
+      <c r="Q119" s="7"/>
+      <c r="R119" s="7">
+        <v>47584</v>
+      </c>
+      <c r="S119" s="7"/>
+      <c r="T119" s="7"/>
+      <c r="U119" s="7"/>
+      <c r="V119" s="7"/>
+      <c r="W119" s="7"/>
+      <c r="X119" s="7"/>
+      <c r="Y119" s="7"/>
+      <c r="Z119" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="AA119" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB119" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28">
+      <c r="A120" s="3">
+        <v>118</v>
+      </c>
+      <c r="B120" s="3">
+        <v>2026080457</v>
+      </c>
+      <c r="C120" s="3">
+        <v>1</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="J120" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="K120" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L120" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="M120" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="N120" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="O120" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P120" s="3"/>
+      <c r="Q120" s="3"/>
+      <c r="R120" s="3">
+        <v>505328</v>
+      </c>
+      <c r="S120" s="3"/>
+      <c r="T120" s="3"/>
+      <c r="U120" s="3"/>
+      <c r="V120" s="3"/>
+      <c r="W120" s="3"/>
+      <c r="X120" s="3"/>
+      <c r="Y120" s="3"/>
+      <c r="Z120" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="AA120" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB120" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28">
+      <c r="A121" s="7">
+        <v>119</v>
+      </c>
+      <c r="B121" s="7">
+        <v>2026080539</v>
+      </c>
+      <c r="C121" s="7">
+        <v>1</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G121" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="H121" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I121" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="J121" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="K121" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="L121" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M121" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="N121" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="O121" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P121" s="7"/>
+      <c r="Q121" s="7"/>
+      <c r="R121" s="7">
+        <v>0</v>
+      </c>
+      <c r="S121" s="7"/>
+      <c r="T121" s="7"/>
+      <c r="U121" s="7"/>
+      <c r="V121" s="7"/>
+      <c r="W121" s="7"/>
+      <c r="X121" s="7"/>
+      <c r="Y121" s="7"/>
+      <c r="Z121" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="AA121" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB121" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28">
+      <c r="A122" s="3">
+        <v>120</v>
+      </c>
+      <c r="B122" s="3">
+        <v>2026081121</v>
+      </c>
+      <c r="C122" s="3">
+        <v>1</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="J122" s="3"/>
+      <c r="K122" s="3"/>
+      <c r="L122" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M122" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="N122" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="O122" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P122" s="3"/>
+      <c r="Q122" s="3"/>
+      <c r="R122" s="3">
+        <v>0</v>
+      </c>
+      <c r="S122" s="3"/>
+      <c r="T122" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U122" s="3"/>
+      <c r="V122" s="3"/>
+      <c r="W122" s="3"/>
+      <c r="X122" s="3"/>
+      <c r="Y122" s="3"/>
+      <c r="Z122" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="AA122" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB122" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28">
+      <c r="A123" s="7">
+        <v>121</v>
+      </c>
+      <c r="B123" s="7">
+        <v>2026080991</v>
+      </c>
+      <c r="C123" s="7">
+        <v>1</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G123" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="I123" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="J123" s="7"/>
+      <c r="K123" s="7"/>
+      <c r="L123" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M123" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="N123" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="O123" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P123" s="7"/>
+      <c r="Q123" s="7"/>
+      <c r="R123" s="7">
+        <v>0</v>
+      </c>
+      <c r="S123" s="7"/>
+      <c r="T123" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="U123" s="7"/>
+      <c r="V123" s="7"/>
+      <c r="W123" s="7"/>
+      <c r="X123" s="7"/>
+      <c r="Y123" s="7"/>
+      <c r="Z123" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="AA123" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB123" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28">
+      <c r="A124" s="3">
         <v>122</v>
       </c>
-      <c r="AA105" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="AB105" s="7"/>
-    </row>
-    <row r="106" spans="1:28">
-      <c r="A106" s="9"/>
-      <c r="B106" s="9"/>
-      <c r="C106" s="9"/>
-      <c r="D106" s="9"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="9"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9"/>
-      <c r="I106" s="9"/>
-      <c r="J106" s="9"/>
-      <c r="K106" s="9"/>
-      <c r="L106" s="10"/>
-      <c r="M106" s="10"/>
-      <c r="N106" s="10"/>
-      <c r="O106" s="9"/>
-      <c r="P106" s="9"/>
-      <c r="Q106" s="9"/>
-      <c r="R106" s="9"/>
-      <c r="S106" s="9"/>
-      <c r="T106" s="9"/>
-      <c r="U106" s="9"/>
-      <c r="V106" s="9"/>
-      <c r="W106" s="9"/>
-      <c r="X106" s="9"/>
-      <c r="Y106" s="9"/>
-      <c r="Z106" s="10"/>
-      <c r="AA106" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="AB106" s="9">
-        <v>70</v>
+      <c r="B124" s="3">
+        <v>2026080058</v>
+      </c>
+      <c r="C124" s="3">
+        <v>1</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L124" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M124" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="N124" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="O124" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P124" s="3"/>
+      <c r="Q124" s="3"/>
+      <c r="R124" s="3">
+        <v>0</v>
+      </c>
+      <c r="S124" s="3"/>
+      <c r="T124" s="3"/>
+      <c r="U124" s="3"/>
+      <c r="V124" s="3"/>
+      <c r="W124" s="3"/>
+      <c r="X124" s="3"/>
+      <c r="Y124" s="3"/>
+      <c r="Z124" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="AA124" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB124" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28">
+      <c r="A125" s="7">
+        <v>123</v>
+      </c>
+      <c r="B125" s="7">
+        <v>2026080239</v>
+      </c>
+      <c r="C125" s="7">
+        <v>1</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="I125" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="J125" s="7"/>
+      <c r="K125" s="7"/>
+      <c r="L125" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M125" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="N125" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="O125" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P125" s="7"/>
+      <c r="Q125" s="7"/>
+      <c r="R125" s="7">
+        <v>0</v>
+      </c>
+      <c r="S125" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T125" s="7"/>
+      <c r="U125" s="7"/>
+      <c r="V125" s="7"/>
+      <c r="W125" s="7"/>
+      <c r="X125" s="7"/>
+      <c r="Y125" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z125" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA125" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB125" s="7"/>
+    </row>
+    <row r="126" spans="1:28">
+      <c r="A126" s="3">
+        <v>124</v>
+      </c>
+      <c r="B126" s="3">
+        <v>2026080059</v>
+      </c>
+      <c r="C126" s="3">
+        <v>1</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K126" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L126" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M126" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="N126" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="O126" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P126" s="3"/>
+      <c r="Q126" s="3"/>
+      <c r="R126" s="3">
+        <v>0</v>
+      </c>
+      <c r="S126" s="3"/>
+      <c r="T126" s="3"/>
+      <c r="U126" s="3"/>
+      <c r="V126" s="3"/>
+      <c r="W126" s="3"/>
+      <c r="X126" s="3"/>
+      <c r="Y126" s="3"/>
+      <c r="Z126" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="AA126" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB126" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:28">
+      <c r="A127" s="7">
+        <v>125</v>
+      </c>
+      <c r="B127" s="7">
+        <v>2026080400</v>
+      </c>
+      <c r="C127" s="7">
+        <v>1</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G127" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H127" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="I127" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="J127" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="K127" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="L127" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M127" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="N127" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="O127" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P127" s="7"/>
+      <c r="Q127" s="7"/>
+      <c r="R127" s="7">
+        <v>0</v>
+      </c>
+      <c r="S127" s="7"/>
+      <c r="T127" s="7"/>
+      <c r="U127" s="7"/>
+      <c r="V127" s="7"/>
+      <c r="W127" s="7"/>
+      <c r="X127" s="7"/>
+      <c r="Y127" s="7"/>
+      <c r="Z127" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="AA127" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB127" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:28">
+      <c r="A128" s="3">
+        <v>126</v>
+      </c>
+      <c r="B128" s="3">
+        <v>2026080406</v>
+      </c>
+      <c r="C128" s="3">
+        <v>1</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="J128" s="3"/>
+      <c r="K128" s="3"/>
+      <c r="L128" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M128" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="N128" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="O128" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P128" s="3"/>
+      <c r="Q128" s="3"/>
+      <c r="R128" s="3">
+        <v>0</v>
+      </c>
+      <c r="S128" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T128" s="3"/>
+      <c r="U128" s="3"/>
+      <c r="V128" s="3"/>
+      <c r="W128" s="3"/>
+      <c r="X128" s="3"/>
+      <c r="Y128" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z128" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA128" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB128" s="3"/>
+    </row>
+    <row r="129" spans="1:28">
+      <c r="A129" s="7">
+        <v>127</v>
+      </c>
+      <c r="B129" s="7">
+        <v>2026081100</v>
+      </c>
+      <c r="C129" s="7">
+        <v>1</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="H129" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="I129" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="J129" s="7"/>
+      <c r="K129" s="7"/>
+      <c r="L129" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="M129" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="N129" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="O129" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="P129" s="7"/>
+      <c r="Q129" s="7"/>
+      <c r="R129" s="7">
+        <v>0</v>
+      </c>
+      <c r="S129" s="7"/>
+      <c r="T129" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="U129" s="7"/>
+      <c r="V129" s="7"/>
+      <c r="W129" s="7"/>
+      <c r="X129" s="7"/>
+      <c r="Y129" s="7"/>
+      <c r="Z129" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="AA129" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB129" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:28">
+      <c r="A130" s="9"/>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
+      <c r="E130" s="9"/>
+      <c r="F130" s="9"/>
+      <c r="G130" s="9"/>
+      <c r="H130" s="9"/>
+      <c r="I130" s="9"/>
+      <c r="J130" s="9"/>
+      <c r="K130" s="9"/>
+      <c r="L130" s="10"/>
+      <c r="M130" s="10"/>
+      <c r="N130" s="10"/>
+      <c r="O130" s="9"/>
+      <c r="P130" s="9"/>
+      <c r="Q130" s="9"/>
+      <c r="R130" s="9"/>
+      <c r="S130" s="9"/>
+      <c r="T130" s="9"/>
+      <c r="U130" s="9"/>
+      <c r="V130" s="9"/>
+      <c r="W130" s="9"/>
+      <c r="X130" s="9"/>
+      <c r="Y130" s="9"/>
+      <c r="Z130" s="10"/>
+      <c r="AA130" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="AB130" s="9">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/IM/202608_Service_Count_Report.xlsx
+++ b/IM/202608_Service_Count_Report.xlsx
@@ -2901,7 +2901,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7">
-        <v>2026081255</v>
+        <v>2026081256</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>88</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7">
@@ -2949,9 +2949,7 @@
       <c r="R11" s="7">
         <v>747</v>
       </c>
-      <c r="S11" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S11" s="7"/>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
@@ -2973,7 +2971,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3">
-        <v>2026081256</v>
+        <v>2026081255</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -3012,7 +3010,7 @@
         <v>88</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3">
@@ -3021,7 +3019,9 @@
       <c r="R12" s="3">
         <v>747</v>
       </c>
-      <c r="S12" s="3"/>
+      <c r="S12" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
@@ -3041,7 +3041,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7">
-        <v>2026080104</v>
+        <v>2026080103</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -3080,7 +3080,7 @@
         <v>93</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7">
@@ -3089,7 +3089,9 @@
       <c r="R13" s="7">
         <v>2644</v>
       </c>
-      <c r="S13" s="7"/>
+      <c r="S13" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
@@ -3111,7 +3113,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="3">
-        <v>2026080103</v>
+        <v>2026080104</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -3150,7 +3152,7 @@
         <v>93</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3">
@@ -3159,9 +3161,7 @@
       <c r="R14" s="3">
         <v>2644</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="S14" s="3"/>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
@@ -6223,7 +6223,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="3">
-        <v>2026080937</v>
+        <v>2026080936</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -6262,7 +6262,7 @@
         <v>253</v>
       </c>
       <c r="O60" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="P60" s="3">
         <v>8160</v>
@@ -6273,7 +6273,9 @@
       <c r="R60" s="3">
         <v>26200</v>
       </c>
-      <c r="S60" s="3"/>
+      <c r="S60" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
@@ -6295,7 +6297,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="7">
-        <v>2026080936</v>
+        <v>2026080937</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -6334,7 +6336,7 @@
         <v>253</v>
       </c>
       <c r="O61" s="7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P61" s="7">
         <v>8160</v>
@@ -6345,9 +6347,7 @@
       <c r="R61" s="7">
         <v>26200</v>
       </c>
-      <c r="S61" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S61" s="7"/>
       <c r="T61" s="7"/>
       <c r="U61" s="7"/>
       <c r="V61" s="7"/>
@@ -8059,7 +8059,7 @@
         <v>85</v>
       </c>
       <c r="B87" s="7">
-        <v>2026080112</v>
+        <v>2026080113</v>
       </c>
       <c r="C87" s="7">
         <v>1</v>
@@ -8098,20 +8098,16 @@
         <v>321</v>
       </c>
       <c r="O87" s="7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P87" s="7"/>
       <c r="Q87" s="7"/>
       <c r="R87" s="7">
         <v>251357</v>
       </c>
-      <c r="S87" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S87" s="7"/>
       <c r="T87" s="7"/>
-      <c r="U87" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="U87" s="7"/>
       <c r="V87" s="7"/>
       <c r="W87" s="7"/>
       <c r="X87" s="7"/>
@@ -8127,7 +8123,7 @@
         <v>86</v>
       </c>
       <c r="B88" s="3">
-        <v>2026080113</v>
+        <v>2026080112</v>
       </c>
       <c r="C88" s="3">
         <v>1</v>
@@ -8166,16 +8162,20 @@
         <v>321</v>
       </c>
       <c r="O88" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="P88" s="3"/>
       <c r="Q88" s="3"/>
       <c r="R88" s="3">
         <v>251357</v>
       </c>
-      <c r="S88" s="3"/>
+      <c r="S88" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T88" s="3"/>
-      <c r="U88" s="3"/>
+      <c r="U88" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="V88" s="3"/>
       <c r="W88" s="3"/>
       <c r="X88" s="3"/>
@@ -14371,7 +14371,7 @@
         <v>178</v>
       </c>
       <c r="B180" s="3">
-        <v>2026081171</v>
+        <v>2026081285</v>
       </c>
       <c r="C180" s="3">
         <v>1</v>
@@ -14394,12 +14394,8 @@
       <c r="I180" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="J180" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="K180" s="3" t="s">
-        <v>191</v>
-      </c>
+      <c r="J180" s="3"/>
+      <c r="K180" s="3"/>
       <c r="L180" s="6" t="s">
         <v>183</v>
       </c>
@@ -14410,14 +14406,16 @@
         <v>575</v>
       </c>
       <c r="O180" s="3" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="P180" s="3"/>
       <c r="Q180" s="3"/>
       <c r="R180" s="3">
         <v>0</v>
       </c>
-      <c r="S180" s="3"/>
+      <c r="S180" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="T180" s="3"/>
       <c r="U180" s="3"/>
       <c r="V180" s="3"/>
@@ -14425,7 +14423,7 @@
       <c r="X180" s="3"/>
       <c r="Y180" s="3"/>
       <c r="Z180" s="6" t="s">
-        <v>576</v>
+        <v>186</v>
       </c>
       <c r="AA180" s="3" t="s">
         <v>40</v>
@@ -14439,7 +14437,7 @@
         <v>179</v>
       </c>
       <c r="B181" s="7">
-        <v>2026081285</v>
+        <v>2026081171</v>
       </c>
       <c r="C181" s="7">
         <v>1</v>
@@ -14462,8 +14460,12 @@
       <c r="I181" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="J181" s="7"/>
-      <c r="K181" s="7"/>
+      <c r="J181" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K181" s="7" t="s">
+        <v>191</v>
+      </c>
       <c r="L181" s="8" t="s">
         <v>183</v>
       </c>
@@ -14474,16 +14476,14 @@
         <v>575</v>
       </c>
       <c r="O181" s="7" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="P181" s="7"/>
       <c r="Q181" s="7"/>
       <c r="R181" s="7">
         <v>0</v>
       </c>
-      <c r="S181" s="7" t="s">
-        <v>40</v>
-      </c>
+      <c r="S181" s="7"/>
       <c r="T181" s="7"/>
       <c r="U181" s="7"/>
       <c r="V181" s="7"/>
@@ -14491,7 +14491,7 @@
       <c r="X181" s="7"/>
       <c r="Y181" s="7"/>
       <c r="Z181" s="8" t="s">
-        <v>186</v>
+        <v>576</v>
       </c>
       <c r="AA181" s="7" t="s">
         <v>40</v>
